--- a/grupos/4AEM - Estadisticos 20222.xlsx
+++ b/grupos/4AEM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="138">
   <si>
     <t>Materia</t>
   </si>
@@ -934,13 +934,13 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <v>9</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>9</v>
@@ -952,7 +952,7 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -997,13 +997,13 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X4">
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z4">
         <v>9</v>
@@ -1015,7 +1015,7 @@
         <v>8</v>
       </c>
       <c r="AC4">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1023,13 +1023,13 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <v>10</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E5">
         <v>10</v>
@@ -1041,7 +1041,7 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -1086,13 +1086,13 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z5">
         <v>10</v>
@@ -1104,7 +1104,7 @@
         <v>10</v>
       </c>
       <c r="AC5">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1112,13 +1112,13 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <v>7</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -1130,7 +1130,7 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -1175,13 +1175,13 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X6">
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z6">
         <v>6</v>
@@ -1193,7 +1193,7 @@
         <v>7</v>
       </c>
       <c r="AC6">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1201,13 +1201,13 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>8</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1219,7 +1219,7 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -1264,13 +1264,13 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z7">
         <v>6</v>
@@ -1282,7 +1282,7 @@
         <v>8</v>
       </c>
       <c r="AC7">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1290,13 +1290,13 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C8">
         <v>9</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E8">
         <v>10</v>
@@ -1308,7 +1308,7 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1353,13 +1353,13 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z8">
         <v>10</v>
@@ -1371,7 +1371,7 @@
         <v>9</v>
       </c>
       <c r="AC8">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1379,13 +1379,13 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C9">
         <v>5</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E9">
         <v>5</v>
@@ -1397,7 +1397,7 @@
         <v>7</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1442,13 +1442,13 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X9">
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z9">
         <v>5</v>
@@ -1460,7 +1460,7 @@
         <v>7</v>
       </c>
       <c r="AC9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1468,13 +1468,13 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C10">
         <v>6</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E10">
         <v>6</v>
@@ -1486,7 +1486,7 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -1531,13 +1531,13 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X10">
         <v>6</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z10">
         <v>6</v>
@@ -1549,7 +1549,7 @@
         <v>8</v>
       </c>
       <c r="AC10">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1557,13 +1557,13 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C11">
         <v>10</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1575,7 +1575,7 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1620,13 +1620,13 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z11">
         <v>10</v>
@@ -1638,7 +1638,7 @@
         <v>9</v>
       </c>
       <c r="AC11">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1646,13 +1646,13 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C12">
         <v>5</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E12">
         <v>5</v>
@@ -1664,7 +1664,7 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1709,13 +1709,13 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X12">
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z12">
         <v>5</v>
@@ -1727,7 +1727,7 @@
         <v>8</v>
       </c>
       <c r="AC12">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1735,13 +1735,13 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C13">
         <v>9</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E13">
         <v>10</v>
@@ -1753,7 +1753,7 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1798,13 +1798,13 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z13">
         <v>10</v>
@@ -1816,7 +1816,7 @@
         <v>9</v>
       </c>
       <c r="AC13">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1824,13 +1824,13 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C14">
         <v>9</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E14">
         <v>8</v>
@@ -1842,7 +1842,7 @@
         <v>8</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -1887,13 +1887,13 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z14">
         <v>8</v>
@@ -1905,7 +1905,7 @@
         <v>8</v>
       </c>
       <c r="AC14">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1913,13 +1913,13 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C15">
         <v>5</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E15">
         <v>5</v>
@@ -1931,7 +1931,7 @@
         <v>5</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -1976,13 +1976,13 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X15">
         <v>5</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z15">
         <v>5</v>
@@ -1994,7 +1994,7 @@
         <v>5</v>
       </c>
       <c r="AC15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -2002,13 +2002,13 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C16">
         <v>6</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E16">
         <v>5</v>
@@ -2020,7 +2020,7 @@
         <v>7</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -2065,13 +2065,13 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z16">
         <v>5</v>
@@ -2083,7 +2083,7 @@
         <v>7</v>
       </c>
       <c r="AC16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2091,13 +2091,13 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C17">
         <v>5</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E17">
         <v>5</v>
@@ -2109,7 +2109,7 @@
         <v>7</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -2154,13 +2154,13 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X17">
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z17">
         <v>5</v>
@@ -2172,7 +2172,7 @@
         <v>7</v>
       </c>
       <c r="AC17">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2180,13 +2180,13 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C18">
         <v>9</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E18">
         <v>7</v>
@@ -2198,7 +2198,7 @@
         <v>7</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -2243,13 +2243,13 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X18">
         <v>9</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z18">
         <v>7</v>
@@ -2261,7 +2261,7 @@
         <v>7</v>
       </c>
       <c r="AC18">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2269,13 +2269,13 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C19">
         <v>8</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E19">
         <v>6</v>
@@ -2287,7 +2287,7 @@
         <v>7</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -2332,13 +2332,13 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z19">
         <v>6</v>
@@ -2350,7 +2350,7 @@
         <v>7</v>
       </c>
       <c r="AC19">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2358,13 +2358,13 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C20">
         <v>9</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E20">
         <v>10</v>
@@ -2376,7 +2376,7 @@
         <v>7</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2421,13 +2421,13 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z20">
         <v>10</v>
@@ -2439,7 +2439,7 @@
         <v>7</v>
       </c>
       <c r="AC20">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2447,13 +2447,13 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C21">
         <v>5</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E21">
         <v>5</v>
@@ -2465,7 +2465,7 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2510,13 +2510,13 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>5</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z21">
         <v>5</v>
@@ -2528,7 +2528,7 @@
         <v>6</v>
       </c>
       <c r="AC21">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2536,13 +2536,13 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C22">
         <v>5</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E22">
         <v>5</v>
@@ -2554,7 +2554,7 @@
         <v>7</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2599,13 +2599,13 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X22">
         <v>5</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z22">
         <v>5</v>
@@ -2617,7 +2617,7 @@
         <v>7</v>
       </c>
       <c r="AC22">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2625,13 +2625,13 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C23">
         <v>9</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -2643,7 +2643,7 @@
         <v>8</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2688,13 +2688,13 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>9</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z23">
         <v>5</v>
@@ -2706,7 +2706,7 @@
         <v>8</v>
       </c>
       <c r="AC23">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2714,13 +2714,13 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C24">
         <v>9</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E24">
         <v>5</v>
@@ -2732,7 +2732,7 @@
         <v>7</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -2777,13 +2777,13 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X24">
         <v>9</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z24">
         <v>5</v>
@@ -2795,7 +2795,7 @@
         <v>7</v>
       </c>
       <c r="AC24">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2803,13 +2803,13 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C25">
         <v>9</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E25">
         <v>10</v>
@@ -2821,7 +2821,7 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -2866,13 +2866,13 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X25">
         <v>9</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z25">
         <v>10</v>
@@ -2884,7 +2884,7 @@
         <v>8</v>
       </c>
       <c r="AC25">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2892,13 +2892,13 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C26">
         <v>9</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E26">
         <v>5</v>
@@ -2910,7 +2910,7 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -2955,13 +2955,13 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X26">
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z26">
         <v>5</v>
@@ -2973,7 +2973,7 @@
         <v>8</v>
       </c>
       <c r="AC26">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2981,13 +2981,13 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C27">
         <v>7</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E27">
         <v>5</v>
@@ -2999,7 +2999,7 @@
         <v>9</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -3044,13 +3044,13 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>7</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z27">
         <v>5</v>
@@ -3062,7 +3062,7 @@
         <v>9</v>
       </c>
       <c r="AC27">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3070,13 +3070,13 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C28">
         <v>9</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -3088,7 +3088,7 @@
         <v>9</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -3133,13 +3133,13 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z28">
         <v>7</v>
@@ -3151,7 +3151,7 @@
         <v>9</v>
       </c>
       <c r="AC28">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3159,13 +3159,13 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C29">
         <v>10</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E29">
         <v>10</v>
@@ -3177,7 +3177,7 @@
         <v>8</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -3222,13 +3222,13 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>10</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z29">
         <v>10</v>
@@ -3240,7 +3240,7 @@
         <v>8</v>
       </c>
       <c r="AC29">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3248,13 +3248,13 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C30">
         <v>10</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E30">
         <v>7</v>
@@ -3266,7 +3266,7 @@
         <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -3311,13 +3311,13 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X30">
         <v>10</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z30">
         <v>7</v>
@@ -3329,7 +3329,7 @@
         <v>9</v>
       </c>
       <c r="AC30">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3337,13 +3337,13 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C31">
         <v>6</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E31">
         <v>5</v>
@@ -3355,7 +3355,7 @@
         <v>8</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -3400,13 +3400,13 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X31">
         <v>6</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z31">
         <v>5</v>
@@ -3418,7 +3418,7 @@
         <v>8</v>
       </c>
       <c r="AC31">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3426,13 +3426,13 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C32">
         <v>9</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E32">
         <v>6</v>
@@ -3444,7 +3444,7 @@
         <v>8</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -3489,13 +3489,13 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X32">
         <v>9</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z32">
         <v>6</v>
@@ -3507,7 +3507,7 @@
         <v>8</v>
       </c>
       <c r="AC32">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3515,13 +3515,13 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C33">
         <v>10</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E33">
         <v>6</v>
@@ -3533,7 +3533,7 @@
         <v>9</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -3578,13 +3578,13 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X33">
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z33">
         <v>6</v>
@@ -3596,7 +3596,7 @@
         <v>9</v>
       </c>
       <c r="AC33">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3604,13 +3604,13 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C34">
         <v>9</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E34">
         <v>10</v>
@@ -3622,7 +3622,7 @@
         <v>8</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -3667,13 +3667,13 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X34">
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z34">
         <v>10</v>
@@ -3685,7 +3685,7 @@
         <v>8</v>
       </c>
       <c r="AC34">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3815,13 +3815,13 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E4">
         <v>106.7</v>
@@ -3833,7 +3833,7 @@
         <v>103.3</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3883,13 +3883,13 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C5">
         <v>100</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E5">
         <v>106.7</v>
@@ -3901,7 +3901,7 @@
         <v>106.7</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3951,13 +3951,13 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C6">
         <v>100</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E6">
         <v>106.7</v>
@@ -3969,7 +3969,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4019,13 +4019,13 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C7">
         <v>90</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E7">
         <v>106.7</v>
@@ -4037,7 +4037,7 @@
         <v>106.7</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4087,13 +4087,13 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C8">
         <v>100</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E8">
         <v>106.7</v>
@@ -4105,7 +4105,7 @@
         <v>103.3</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4155,13 +4155,13 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C9">
         <v>60</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E9">
         <v>106.7</v>
@@ -4173,7 +4173,7 @@
         <v>110</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -4223,13 +4223,13 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C10">
         <v>95</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E10">
         <v>106.7</v>
@@ -4241,7 +4241,7 @@
         <v>106.7</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -4291,13 +4291,13 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C11">
         <v>100</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>106.7</v>
@@ -4309,7 +4309,7 @@
         <v>103.3</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -4359,13 +4359,13 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C12">
         <v>65</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E12">
         <v>86.7</v>
@@ -4377,7 +4377,7 @@
         <v>103.3</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -4427,13 +4427,13 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C13">
         <v>85</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E13">
         <v>106.7</v>
@@ -4445,7 +4445,7 @@
         <v>106.7</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -4495,13 +4495,13 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C14">
         <v>100</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>106.7</v>
@@ -4513,7 +4513,7 @@
         <v>100</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -4563,13 +4563,13 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="C15">
         <v>65</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E15">
         <v>80</v>
@@ -4581,7 +4581,7 @@
         <v>93.3</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -4631,13 +4631,13 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C16">
         <v>85</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E16">
         <v>86.7</v>
@@ -4649,7 +4649,7 @@
         <v>106.7</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -4699,13 +4699,13 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="C17">
         <v>75</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E17">
         <v>86.7</v>
@@ -4717,7 +4717,7 @@
         <v>106.7</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -4767,13 +4767,13 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C18">
         <v>100</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E18">
         <v>106.7</v>
@@ -4785,7 +4785,7 @@
         <v>103.3</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -4835,13 +4835,13 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C19">
         <v>85</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E19">
         <v>106.7</v>
@@ -4853,7 +4853,7 @@
         <v>100</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -4903,13 +4903,13 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C20">
         <v>100</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20">
         <v>106.7</v>
@@ -4921,7 +4921,7 @@
         <v>100</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -4971,13 +4971,13 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C21">
         <v>80</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E21">
         <v>106.7</v>
@@ -4989,7 +4989,7 @@
         <v>103.3</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -5039,13 +5039,13 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C22">
         <v>80</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E22">
         <v>86.7</v>
@@ -5057,7 +5057,7 @@
         <v>106.7</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -5107,13 +5107,13 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C23">
         <v>100</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E23">
         <v>106.7</v>
@@ -5125,7 +5125,7 @@
         <v>106.7</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -5175,13 +5175,13 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="C24">
         <v>90</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24">
         <v>106.7</v>
@@ -5193,7 +5193,7 @@
         <v>103.3</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -5243,13 +5243,13 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C25">
         <v>100</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E25">
         <v>106.7</v>
@@ -5261,7 +5261,7 @@
         <v>106.7</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -5311,13 +5311,13 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C26">
         <v>100</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E26">
         <v>106.7</v>
@@ -5329,7 +5329,7 @@
         <v>103.3</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -5379,13 +5379,13 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C27">
         <v>100</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E27">
         <v>106.7</v>
@@ -5397,7 +5397,7 @@
         <v>100</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -5447,13 +5447,13 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C28">
         <v>100</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E28">
         <v>106.7</v>
@@ -5465,7 +5465,7 @@
         <v>106.7</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -5515,13 +5515,13 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C29">
         <v>100</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E29">
         <v>106.7</v>
@@ -5533,7 +5533,7 @@
         <v>103.3</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -5583,13 +5583,13 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C30">
         <v>100</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E30">
         <v>106.7</v>
@@ -5601,7 +5601,7 @@
         <v>103.3</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -5651,13 +5651,13 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C31">
         <v>75</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E31">
         <v>106.7</v>
@@ -5669,7 +5669,7 @@
         <v>100</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -5719,13 +5719,13 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C32">
         <v>100</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32">
         <v>106.7</v>
@@ -5737,7 +5737,7 @@
         <v>100</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -5787,13 +5787,13 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C33">
         <v>100</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E33">
         <v>106.7</v>
@@ -5805,7 +5805,7 @@
         <v>103.3</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -5855,13 +5855,13 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C34">
         <v>100</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E34">
         <v>106.7</v>
@@ -5873,7 +5873,7 @@
         <v>106.7</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -5970,7 +5970,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>
@@ -5979,22 +5979,25 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>61.29</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>38.71</v>
+      </c>
+      <c r="H2">
+        <v>6.9</v>
       </c>
       <c r="I2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6008,22 +6011,25 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>74.19</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>25.81</v>
+      </c>
+      <c r="H3">
+        <v>6.1</v>
       </c>
       <c r="I3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -6037,27 +6043,30 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>74.19</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>25.81</v>
+      </c>
+      <c r="H4">
+        <v>6.8</v>
       </c>
       <c r="I4">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -6066,19 +6075,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>61.29</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="G5">
-        <v>38.71</v>
+        <v>19.35</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6089,7 +6098,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
@@ -6098,19 +6107,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>80.65000000000001</v>
+        <v>96.77</v>
       </c>
       <c r="G6">
-        <v>19.35</v>
+        <v>3.23</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6121,7 +6130,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>56</v>
@@ -6142,7 +6151,7 @@
         <v>3.23</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6153,7 +6162,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>56</v>
@@ -6162,19 +6171,19 @@
         <v>31</v>
       </c>
       <c r="D8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>96.77</v>
+        <v>100</v>
       </c>
       <c r="G8">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6190,7 +6199,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6215,1866 +6224,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920151</v>
-      </c>
-      <c r="B2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920151</v>
-      </c>
-      <c r="B3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" t="s">
-        <v>109</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920151</v>
-      </c>
-      <c r="B4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920152</v>
-      </c>
-      <c r="B5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920152</v>
-      </c>
-      <c r="B6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920152</v>
-      </c>
-      <c r="B7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" t="s">
-        <v>110</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920153</v>
-      </c>
-      <c r="B8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D8" t="s">
-        <v>111</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920153</v>
-      </c>
-      <c r="B9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" t="s">
-        <v>91</v>
-      </c>
-      <c r="D9" t="s">
-        <v>111</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920153</v>
-      </c>
-      <c r="B10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D10" t="s">
-        <v>111</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920154</v>
-      </c>
-      <c r="B11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D11" t="s">
-        <v>112</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920154</v>
-      </c>
-      <c r="B12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" t="s">
-        <v>92</v>
-      </c>
-      <c r="D12" t="s">
-        <v>112</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920154</v>
-      </c>
-      <c r="B13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" t="s">
-        <v>92</v>
-      </c>
-      <c r="D13" t="s">
-        <v>112</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920155</v>
-      </c>
-      <c r="B14" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" t="s">
-        <v>93</v>
-      </c>
-      <c r="D14" t="s">
-        <v>113</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920155</v>
-      </c>
-      <c r="B15" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920155</v>
-      </c>
-      <c r="B16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" t="s">
-        <v>93</v>
-      </c>
-      <c r="D16" t="s">
-        <v>113</v>
-      </c>
-      <c r="E16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920156</v>
-      </c>
-      <c r="B17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" t="s">
-        <v>94</v>
-      </c>
-      <c r="D17" t="s">
-        <v>114</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920156</v>
-      </c>
-      <c r="B18" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18" t="s">
-        <v>114</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920156</v>
-      </c>
-      <c r="B19" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" t="s">
-        <v>114</v>
-      </c>
-      <c r="E19" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920157</v>
-      </c>
-      <c r="B20" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" t="s">
-        <v>115</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920157</v>
-      </c>
-      <c r="B21" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" t="s">
-        <v>95</v>
-      </c>
-      <c r="D21" t="s">
-        <v>115</v>
-      </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920157</v>
-      </c>
-      <c r="B22" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" t="s">
-        <v>95</v>
-      </c>
-      <c r="D22" t="s">
-        <v>115</v>
-      </c>
-      <c r="E22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920158</v>
-      </c>
-      <c r="B23" t="s">
-        <v>68</v>
-      </c>
-      <c r="C23" t="s">
-        <v>96</v>
-      </c>
-      <c r="D23" t="s">
-        <v>116</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920158</v>
-      </c>
-      <c r="B24" t="s">
-        <v>68</v>
-      </c>
-      <c r="C24" t="s">
-        <v>96</v>
-      </c>
-      <c r="D24" t="s">
-        <v>116</v>
-      </c>
-      <c r="E24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920158</v>
-      </c>
-      <c r="B25" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" t="s">
-        <v>96</v>
-      </c>
-      <c r="D25" t="s">
-        <v>116</v>
-      </c>
-      <c r="E25" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920159</v>
-      </c>
-      <c r="B26" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" t="s">
-        <v>91</v>
-      </c>
-      <c r="D26" t="s">
-        <v>117</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920159</v>
-      </c>
-      <c r="B27" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" t="s">
-        <v>91</v>
-      </c>
-      <c r="D27" t="s">
-        <v>117</v>
-      </c>
-      <c r="E27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920159</v>
-      </c>
-      <c r="B28" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" t="s">
-        <v>91</v>
-      </c>
-      <c r="D28" t="s">
-        <v>117</v>
-      </c>
-      <c r="E28" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920160</v>
-      </c>
-      <c r="B29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" t="s">
-        <v>63</v>
-      </c>
-      <c r="D29" t="s">
-        <v>118</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920160</v>
-      </c>
-      <c r="B30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D30" t="s">
-        <v>118</v>
-      </c>
-      <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920160</v>
-      </c>
-      <c r="B31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C31" t="s">
-        <v>63</v>
-      </c>
-      <c r="D31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920161</v>
-      </c>
-      <c r="B32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" t="s">
-        <v>97</v>
-      </c>
-      <c r="D32" t="s">
-        <v>119</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920161</v>
-      </c>
-      <c r="B33" t="s">
-        <v>70</v>
-      </c>
-      <c r="C33" t="s">
-        <v>97</v>
-      </c>
-      <c r="D33" t="s">
-        <v>119</v>
-      </c>
-      <c r="E33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920161</v>
-      </c>
-      <c r="B34" t="s">
-        <v>70</v>
-      </c>
-      <c r="C34" t="s">
-        <v>97</v>
-      </c>
-      <c r="D34" t="s">
-        <v>119</v>
-      </c>
-      <c r="E34" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920162</v>
-      </c>
-      <c r="B35" t="s">
-        <v>71</v>
-      </c>
-      <c r="C35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D35" t="s">
-        <v>120</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920162</v>
-      </c>
-      <c r="B36" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D36" t="s">
-        <v>120</v>
-      </c>
-      <c r="E36" t="s">
-        <v>5</v>
-      </c>
-      <c r="F36" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920162</v>
-      </c>
-      <c r="B37" t="s">
-        <v>71</v>
-      </c>
-      <c r="C37" t="s">
-        <v>70</v>
-      </c>
-      <c r="D37" t="s">
-        <v>120</v>
-      </c>
-      <c r="E37" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920163</v>
-      </c>
-      <c r="B38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C38" t="s">
-        <v>92</v>
-      </c>
-      <c r="D38" t="s">
-        <v>121</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920163</v>
-      </c>
-      <c r="B39" t="s">
-        <v>72</v>
-      </c>
-      <c r="C39" t="s">
-        <v>92</v>
-      </c>
-      <c r="D39" t="s">
-        <v>121</v>
-      </c>
-      <c r="E39" t="s">
-        <v>5</v>
-      </c>
-      <c r="F39" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920163</v>
-      </c>
-      <c r="B40" t="s">
-        <v>72</v>
-      </c>
-      <c r="C40" t="s">
-        <v>92</v>
-      </c>
-      <c r="D40" t="s">
-        <v>121</v>
-      </c>
-      <c r="E40" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920164</v>
-      </c>
-      <c r="B41" t="s">
-        <v>73</v>
-      </c>
-      <c r="C41" t="s">
-        <v>98</v>
-      </c>
-      <c r="D41" t="s">
-        <v>122</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920164</v>
-      </c>
-      <c r="B42" t="s">
-        <v>73</v>
-      </c>
-      <c r="C42" t="s">
-        <v>98</v>
-      </c>
-      <c r="D42" t="s">
-        <v>122</v>
-      </c>
-      <c r="E42" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051920164</v>
-      </c>
-      <c r="B43" t="s">
-        <v>73</v>
-      </c>
-      <c r="C43" t="s">
-        <v>98</v>
-      </c>
-      <c r="D43" t="s">
-        <v>122</v>
-      </c>
-      <c r="E43" t="s">
-        <v>11</v>
-      </c>
-      <c r="F43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>21330051920165</v>
-      </c>
-      <c r="B44" t="s">
-        <v>74</v>
-      </c>
-      <c r="C44" t="s">
-        <v>99</v>
-      </c>
-      <c r="D44" t="s">
-        <v>123</v>
-      </c>
-      <c r="E44" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>21330051920165</v>
-      </c>
-      <c r="B45" t="s">
-        <v>74</v>
-      </c>
-      <c r="C45" t="s">
-        <v>99</v>
-      </c>
-      <c r="D45" t="s">
-        <v>123</v>
-      </c>
-      <c r="E45" t="s">
-        <v>5</v>
-      </c>
-      <c r="F45" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>21330051920165</v>
-      </c>
-      <c r="B46" t="s">
-        <v>74</v>
-      </c>
-      <c r="C46" t="s">
-        <v>99</v>
-      </c>
-      <c r="D46" t="s">
-        <v>123</v>
-      </c>
-      <c r="E46" t="s">
-        <v>11</v>
-      </c>
-      <c r="F46" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>21330051920166</v>
-      </c>
-      <c r="B47" t="s">
-        <v>75</v>
-      </c>
-      <c r="C47" t="s">
-        <v>100</v>
-      </c>
-      <c r="D47" t="s">
-        <v>124</v>
-      </c>
-      <c r="E47" t="s">
-        <v>7</v>
-      </c>
-      <c r="F47" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>21330051920166</v>
-      </c>
-      <c r="B48" t="s">
-        <v>75</v>
-      </c>
-      <c r="C48" t="s">
-        <v>100</v>
-      </c>
-      <c r="D48" t="s">
-        <v>124</v>
-      </c>
-      <c r="E48" t="s">
-        <v>5</v>
-      </c>
-      <c r="F48" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>21330051920166</v>
-      </c>
-      <c r="B49" t="s">
-        <v>75</v>
-      </c>
-      <c r="C49" t="s">
-        <v>100</v>
-      </c>
-      <c r="D49" t="s">
-        <v>124</v>
-      </c>
-      <c r="E49" t="s">
-        <v>11</v>
-      </c>
-      <c r="F49" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>21330051920167</v>
-      </c>
-      <c r="B50" t="s">
-        <v>76</v>
-      </c>
-      <c r="C50" t="s">
-        <v>101</v>
-      </c>
-      <c r="D50" t="s">
-        <v>125</v>
-      </c>
-      <c r="E50" t="s">
-        <v>7</v>
-      </c>
-      <c r="F50" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>21330051920167</v>
-      </c>
-      <c r="B51" t="s">
-        <v>76</v>
-      </c>
-      <c r="C51" t="s">
-        <v>101</v>
-      </c>
-      <c r="D51" t="s">
-        <v>125</v>
-      </c>
-      <c r="E51" t="s">
-        <v>5</v>
-      </c>
-      <c r="F51" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>21330051920167</v>
-      </c>
-      <c r="B52" t="s">
-        <v>76</v>
-      </c>
-      <c r="C52" t="s">
-        <v>101</v>
-      </c>
-      <c r="D52" t="s">
-        <v>125</v>
-      </c>
-      <c r="E52" t="s">
-        <v>11</v>
-      </c>
-      <c r="F52" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>21330051920168</v>
-      </c>
-      <c r="B53" t="s">
-        <v>77</v>
-      </c>
-      <c r="C53" t="s">
-        <v>72</v>
-      </c>
-      <c r="D53" t="s">
-        <v>126</v>
-      </c>
-      <c r="E53" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>21330051920168</v>
-      </c>
-      <c r="B54" t="s">
-        <v>77</v>
-      </c>
-      <c r="C54" t="s">
-        <v>72</v>
-      </c>
-      <c r="D54" t="s">
-        <v>126</v>
-      </c>
-      <c r="E54" t="s">
-        <v>5</v>
-      </c>
-      <c r="F54" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>21330051920168</v>
-      </c>
-      <c r="B55" t="s">
-        <v>77</v>
-      </c>
-      <c r="C55" t="s">
-        <v>72</v>
-      </c>
-      <c r="D55" t="s">
-        <v>126</v>
-      </c>
-      <c r="E55" t="s">
-        <v>11</v>
-      </c>
-      <c r="F55" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>21330051920169</v>
-      </c>
-      <c r="B56" t="s">
-        <v>78</v>
-      </c>
-      <c r="C56" t="s">
-        <v>71</v>
-      </c>
-      <c r="D56" t="s">
-        <v>127</v>
-      </c>
-      <c r="E56" t="s">
-        <v>7</v>
-      </c>
-      <c r="F56" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>21330051920169</v>
-      </c>
-      <c r="B57" t="s">
-        <v>78</v>
-      </c>
-      <c r="C57" t="s">
-        <v>71</v>
-      </c>
-      <c r="D57" t="s">
-        <v>127</v>
-      </c>
-      <c r="E57" t="s">
-        <v>5</v>
-      </c>
-      <c r="F57" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>21330051920169</v>
-      </c>
-      <c r="B58" t="s">
-        <v>78</v>
-      </c>
-      <c r="C58" t="s">
-        <v>71</v>
-      </c>
-      <c r="D58" t="s">
-        <v>127</v>
-      </c>
-      <c r="E58" t="s">
-        <v>11</v>
-      </c>
-      <c r="F58" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>21330051920170</v>
-      </c>
-      <c r="B59" t="s">
-        <v>78</v>
-      </c>
-      <c r="C59" t="s">
-        <v>88</v>
-      </c>
-      <c r="D59" t="s">
-        <v>128</v>
-      </c>
-      <c r="E59" t="s">
-        <v>7</v>
-      </c>
-      <c r="F59" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>21330051920170</v>
-      </c>
-      <c r="B60" t="s">
-        <v>78</v>
-      </c>
-      <c r="C60" t="s">
-        <v>88</v>
-      </c>
-      <c r="D60" t="s">
-        <v>128</v>
-      </c>
-      <c r="E60" t="s">
-        <v>5</v>
-      </c>
-      <c r="F60" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>21330051920170</v>
-      </c>
-      <c r="B61" t="s">
-        <v>78</v>
-      </c>
-      <c r="C61" t="s">
-        <v>88</v>
-      </c>
-      <c r="D61" t="s">
-        <v>128</v>
-      </c>
-      <c r="E61" t="s">
-        <v>11</v>
-      </c>
-      <c r="F61" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>21330051920171</v>
-      </c>
-      <c r="B62" t="s">
-        <v>79</v>
-      </c>
-      <c r="C62" t="s">
-        <v>78</v>
-      </c>
-      <c r="D62" t="s">
-        <v>129</v>
-      </c>
-      <c r="E62" t="s">
-        <v>7</v>
-      </c>
-      <c r="F62" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>21330051920171</v>
-      </c>
-      <c r="B63" t="s">
-        <v>79</v>
-      </c>
-      <c r="C63" t="s">
-        <v>78</v>
-      </c>
-      <c r="D63" t="s">
-        <v>129</v>
-      </c>
-      <c r="E63" t="s">
-        <v>5</v>
-      </c>
-      <c r="F63" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>21330051920171</v>
-      </c>
-      <c r="B64" t="s">
-        <v>79</v>
-      </c>
-      <c r="C64" t="s">
-        <v>78</v>
-      </c>
-      <c r="D64" t="s">
-        <v>129</v>
-      </c>
-      <c r="E64" t="s">
-        <v>11</v>
-      </c>
-      <c r="F64" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>21330051920173</v>
-      </c>
-      <c r="B65" t="s">
-        <v>80</v>
-      </c>
-      <c r="C65" t="s">
-        <v>102</v>
-      </c>
-      <c r="D65" t="s">
-        <v>130</v>
-      </c>
-      <c r="E65" t="s">
-        <v>7</v>
-      </c>
-      <c r="F65" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>21330051920173</v>
-      </c>
-      <c r="B66" t="s">
-        <v>80</v>
-      </c>
-      <c r="C66" t="s">
-        <v>102</v>
-      </c>
-      <c r="D66" t="s">
-        <v>130</v>
-      </c>
-      <c r="E66" t="s">
-        <v>5</v>
-      </c>
-      <c r="F66" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>21330051920173</v>
-      </c>
-      <c r="B67" t="s">
-        <v>80</v>
-      </c>
-      <c r="C67" t="s">
-        <v>102</v>
-      </c>
-      <c r="D67" t="s">
-        <v>130</v>
-      </c>
-      <c r="E67" t="s">
-        <v>11</v>
-      </c>
-      <c r="F67" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>21330051920175</v>
-      </c>
-      <c r="B68" t="s">
-        <v>81</v>
-      </c>
-      <c r="C68" t="s">
-        <v>103</v>
-      </c>
-      <c r="D68" t="s">
-        <v>131</v>
-      </c>
-      <c r="E68" t="s">
-        <v>7</v>
-      </c>
-      <c r="F68" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>21330051920175</v>
-      </c>
-      <c r="B69" t="s">
-        <v>81</v>
-      </c>
-      <c r="C69" t="s">
-        <v>103</v>
-      </c>
-      <c r="D69" t="s">
-        <v>131</v>
-      </c>
-      <c r="E69" t="s">
-        <v>5</v>
-      </c>
-      <c r="F69" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>21330051920175</v>
-      </c>
-      <c r="B70" t="s">
-        <v>81</v>
-      </c>
-      <c r="C70" t="s">
-        <v>103</v>
-      </c>
-      <c r="D70" t="s">
-        <v>131</v>
-      </c>
-      <c r="E70" t="s">
-        <v>11</v>
-      </c>
-      <c r="F70" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>21330051920176</v>
-      </c>
-      <c r="B71" t="s">
-        <v>82</v>
-      </c>
-      <c r="C71" t="s">
-        <v>104</v>
-      </c>
-      <c r="D71" t="s">
-        <v>132</v>
-      </c>
-      <c r="E71" t="s">
-        <v>7</v>
-      </c>
-      <c r="F71" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>21330051920176</v>
-      </c>
-      <c r="B72" t="s">
-        <v>82</v>
-      </c>
-      <c r="C72" t="s">
-        <v>104</v>
-      </c>
-      <c r="D72" t="s">
-        <v>132</v>
-      </c>
-      <c r="E72" t="s">
-        <v>5</v>
-      </c>
-      <c r="F72" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>21330051920176</v>
-      </c>
-      <c r="B73" t="s">
-        <v>82</v>
-      </c>
-      <c r="C73" t="s">
-        <v>104</v>
-      </c>
-      <c r="D73" t="s">
-        <v>132</v>
-      </c>
-      <c r="E73" t="s">
-        <v>11</v>
-      </c>
-      <c r="F73" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>21330051920178</v>
-      </c>
-      <c r="B74" t="s">
-        <v>83</v>
-      </c>
-      <c r="C74" t="s">
-        <v>105</v>
-      </c>
-      <c r="D74" t="s">
-        <v>133</v>
-      </c>
-      <c r="E74" t="s">
-        <v>7</v>
-      </c>
-      <c r="F74" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>21330051920178</v>
-      </c>
-      <c r="B75" t="s">
-        <v>83</v>
-      </c>
-      <c r="C75" t="s">
-        <v>105</v>
-      </c>
-      <c r="D75" t="s">
-        <v>133</v>
-      </c>
-      <c r="E75" t="s">
-        <v>5</v>
-      </c>
-      <c r="F75" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>21330051920178</v>
-      </c>
-      <c r="B76" t="s">
-        <v>83</v>
-      </c>
-      <c r="C76" t="s">
-        <v>105</v>
-      </c>
-      <c r="D76" t="s">
-        <v>133</v>
-      </c>
-      <c r="E76" t="s">
-        <v>11</v>
-      </c>
-      <c r="F76" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>21330051920179</v>
-      </c>
-      <c r="B77" t="s">
-        <v>84</v>
-      </c>
-      <c r="C77" t="s">
-        <v>106</v>
-      </c>
-      <c r="D77" t="s">
-        <v>134</v>
-      </c>
-      <c r="E77" t="s">
-        <v>7</v>
-      </c>
-      <c r="F77" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>21330051920179</v>
-      </c>
-      <c r="B78" t="s">
-        <v>84</v>
-      </c>
-      <c r="C78" t="s">
-        <v>106</v>
-      </c>
-      <c r="D78" t="s">
-        <v>134</v>
-      </c>
-      <c r="E78" t="s">
-        <v>5</v>
-      </c>
-      <c r="F78" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>21330051920179</v>
-      </c>
-      <c r="B79" t="s">
-        <v>84</v>
-      </c>
-      <c r="C79" t="s">
-        <v>106</v>
-      </c>
-      <c r="D79" t="s">
-        <v>134</v>
-      </c>
-      <c r="E79" t="s">
-        <v>11</v>
-      </c>
-      <c r="F79" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>21330051920180</v>
-      </c>
-      <c r="B80" t="s">
-        <v>85</v>
-      </c>
-      <c r="C80" t="s">
-        <v>69</v>
-      </c>
-      <c r="D80" t="s">
-        <v>135</v>
-      </c>
-      <c r="E80" t="s">
-        <v>7</v>
-      </c>
-      <c r="F80" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>21330051920180</v>
-      </c>
-      <c r="B81" t="s">
-        <v>85</v>
-      </c>
-      <c r="C81" t="s">
-        <v>69</v>
-      </c>
-      <c r="D81" t="s">
-        <v>135</v>
-      </c>
-      <c r="E81" t="s">
-        <v>5</v>
-      </c>
-      <c r="F81" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>21330051920180</v>
-      </c>
-      <c r="B82" t="s">
-        <v>85</v>
-      </c>
-      <c r="C82" t="s">
-        <v>69</v>
-      </c>
-      <c r="D82" t="s">
-        <v>135</v>
-      </c>
-      <c r="E82" t="s">
-        <v>11</v>
-      </c>
-      <c r="F82" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>21330051920181</v>
-      </c>
-      <c r="B83" t="s">
-        <v>86</v>
-      </c>
-      <c r="C83" t="s">
-        <v>107</v>
-      </c>
-      <c r="D83" t="s">
-        <v>136</v>
-      </c>
-      <c r="E83" t="s">
-        <v>7</v>
-      </c>
-      <c r="F83" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>21330051920181</v>
-      </c>
-      <c r="B84" t="s">
-        <v>86</v>
-      </c>
-      <c r="C84" t="s">
-        <v>107</v>
-      </c>
-      <c r="D84" t="s">
-        <v>136</v>
-      </c>
-      <c r="E84" t="s">
-        <v>5</v>
-      </c>
-      <c r="F84" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>21330051920181</v>
-      </c>
-      <c r="B85" t="s">
-        <v>86</v>
-      </c>
-      <c r="C85" t="s">
-        <v>107</v>
-      </c>
-      <c r="D85" t="s">
-        <v>136</v>
-      </c>
-      <c r="E85" t="s">
-        <v>11</v>
-      </c>
-      <c r="F85" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>21330051920182</v>
-      </c>
-      <c r="B86" t="s">
-        <v>87</v>
-      </c>
-      <c r="C86" t="s">
-        <v>78</v>
-      </c>
-      <c r="D86" t="s">
-        <v>137</v>
-      </c>
-      <c r="E86" t="s">
-        <v>7</v>
-      </c>
-      <c r="F86" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>21330051920182</v>
-      </c>
-      <c r="B87" t="s">
-        <v>87</v>
-      </c>
-      <c r="C87" t="s">
-        <v>78</v>
-      </c>
-      <c r="D87" t="s">
-        <v>137</v>
-      </c>
-      <c r="E87" t="s">
-        <v>5</v>
-      </c>
-      <c r="F87" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>21330051920182</v>
-      </c>
-      <c r="B88" t="s">
-        <v>87</v>
-      </c>
-      <c r="C88" t="s">
-        <v>78</v>
-      </c>
-      <c r="D88" t="s">
-        <v>137</v>
-      </c>
-      <c r="E88" t="s">
-        <v>11</v>
-      </c>
-      <c r="F88" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>21330051920183</v>
-      </c>
-      <c r="B89" t="s">
-        <v>87</v>
-      </c>
-      <c r="C89" t="s">
-        <v>108</v>
-      </c>
-      <c r="D89" t="s">
-        <v>124</v>
-      </c>
-      <c r="E89" t="s">
-        <v>7</v>
-      </c>
-      <c r="F89" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>21330051920183</v>
-      </c>
-      <c r="B90" t="s">
-        <v>87</v>
-      </c>
-      <c r="C90" t="s">
-        <v>108</v>
-      </c>
-      <c r="D90" t="s">
-        <v>124</v>
-      </c>
-      <c r="E90" t="s">
-        <v>5</v>
-      </c>
-      <c r="F90" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>21330051920183</v>
-      </c>
-      <c r="B91" t="s">
-        <v>87</v>
-      </c>
-      <c r="C91" t="s">
-        <v>108</v>
-      </c>
-      <c r="D91" t="s">
-        <v>124</v>
-      </c>
-      <c r="E91" t="s">
-        <v>11</v>
-      </c>
-      <c r="F91" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>21330051920184</v>
-      </c>
-      <c r="B92" t="s">
-        <v>88</v>
-      </c>
-      <c r="C92" t="s">
-        <v>86</v>
-      </c>
-      <c r="D92" t="s">
-        <v>109</v>
-      </c>
-      <c r="E92" t="s">
-        <v>7</v>
-      </c>
-      <c r="F92" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>21330051920184</v>
-      </c>
-      <c r="B93" t="s">
-        <v>88</v>
-      </c>
-      <c r="C93" t="s">
-        <v>86</v>
-      </c>
-      <c r="D93" t="s">
-        <v>109</v>
-      </c>
-      <c r="E93" t="s">
-        <v>5</v>
-      </c>
-      <c r="F93" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>21330051920184</v>
-      </c>
-      <c r="B94" t="s">
-        <v>88</v>
-      </c>
-      <c r="C94" t="s">
-        <v>86</v>
-      </c>
-      <c r="D94" t="s">
-        <v>109</v>
-      </c>
-      <c r="E94" t="s">
-        <v>11</v>
-      </c>
-      <c r="F94" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -8122,7 +6271,7 @@
         <v>109</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -8139,7 +6288,7 @@
         <v>110</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -8156,7 +6305,7 @@
         <v>111</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -8173,7 +6322,7 @@
         <v>112</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -8190,7 +6339,7 @@
         <v>113</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -8207,7 +6356,7 @@
         <v>114</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -8224,7 +6373,7 @@
         <v>115</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -8241,7 +6390,7 @@
         <v>116</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -8258,7 +6407,7 @@
         <v>117</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -8275,7 +6424,7 @@
         <v>118</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -8292,7 +6441,7 @@
         <v>119</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -8309,7 +6458,7 @@
         <v>120</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -8326,7 +6475,7 @@
         <v>121</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -8343,7 +6492,7 @@
         <v>122</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -8360,7 +6509,7 @@
         <v>123</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -8377,7 +6526,7 @@
         <v>124</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -8394,7 +6543,7 @@
         <v>125</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -8411,7 +6560,7 @@
         <v>126</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -8428,7 +6577,7 @@
         <v>127</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -8445,7 +6594,7 @@
         <v>128</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -8462,7 +6611,7 @@
         <v>129</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -8479,7 +6628,7 @@
         <v>130</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -8496,7 +6645,7 @@
         <v>131</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -8513,7 +6662,7 @@
         <v>132</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -8530,7 +6679,7 @@
         <v>133</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -8547,7 +6696,7 @@
         <v>134</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -8564,7 +6713,7 @@
         <v>135</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -8581,7 +6730,7 @@
         <v>136</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -8598,7 +6747,7 @@
         <v>137</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -8615,7 +6764,7 @@
         <v>124</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -8632,7 +6781,7 @@
         <v>109</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8642,7 +6791,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8672,6 +6821,236 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920163</v>
+      </c>
+      <c r="B2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920163</v>
+      </c>
+      <c r="B3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920171</v>
+      </c>
+      <c r="B4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920171</v>
+      </c>
+      <c r="B5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920176</v>
+      </c>
+      <c r="B6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920176</v>
+      </c>
+      <c r="B7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" t="s">
+        <v>132</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920156</v>
+      </c>
+      <c r="B8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920164</v>
+      </c>
+      <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" t="s">
+        <v>122</v>
+      </c>
+      <c r="E9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920170</v>
+      </c>
+      <c r="B10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" t="s">
+        <v>128</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920181</v>
+      </c>
+      <c r="B11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" t="s">
+        <v>136</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/4AEM - Estadisticos 20222.xlsx
+++ b/grupos/4AEM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="143">
   <si>
     <t>Materia</t>
   </si>
@@ -189,7 +189,22 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
+    <t>Torres Sánchez José Luis</t>
+  </si>
+  <si>
+    <t>Medina Tolentino Elio</t>
   </si>
   <si>
     <t>NC</t>
@@ -6005,7 +6020,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C3">
         <v>31</v>
@@ -6037,7 +6052,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C4">
         <v>31</v>
@@ -6069,7 +6084,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C5">
         <v>31</v>
@@ -6101,7 +6116,7 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C6">
         <v>31</v>
@@ -6133,7 +6148,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C7">
         <v>31</v>
@@ -6165,7 +6180,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C8">
         <v>31</v>
@@ -6208,16 +6223,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -6242,16 +6257,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>54</v>
@@ -6262,13 +6277,13 @@
         <v>21330051920151</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -6279,13 +6294,13 @@
         <v>21330051920152</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -6296,13 +6311,13 @@
         <v>21330051920153</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -6313,13 +6328,13 @@
         <v>21330051920154</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -6330,13 +6345,13 @@
         <v>21330051920155</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -6347,13 +6362,13 @@
         <v>21330051920156</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -6364,13 +6379,13 @@
         <v>21330051920157</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -6381,13 +6396,13 @@
         <v>21330051920158</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -6398,13 +6413,13 @@
         <v>21330051920159</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -6415,13 +6430,13 @@
         <v>21330051920160</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -6432,13 +6447,13 @@
         <v>21330051920161</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -6449,13 +6464,13 @@
         <v>21330051920162</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D13" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -6466,13 +6481,13 @@
         <v>21330051920163</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D14" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -6483,13 +6498,13 @@
         <v>21330051920164</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -6500,13 +6515,13 @@
         <v>21330051920165</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -6517,13 +6532,13 @@
         <v>21330051920166</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D17" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -6534,13 +6549,13 @@
         <v>21330051920167</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D18" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -6551,13 +6566,13 @@
         <v>21330051920168</v>
       </c>
       <c r="B19" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" t="s">
         <v>77</v>
       </c>
-      <c r="C19" t="s">
-        <v>72</v>
-      </c>
       <c r="D19" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -6568,13 +6583,13 @@
         <v>21330051920169</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -6585,13 +6600,13 @@
         <v>21330051920170</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -6602,13 +6617,13 @@
         <v>21330051920171</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D22" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -6619,13 +6634,13 @@
         <v>21330051920173</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D23" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -6636,13 +6651,13 @@
         <v>21330051920175</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D24" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -6653,13 +6668,13 @@
         <v>21330051920176</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D25" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -6670,13 +6685,13 @@
         <v>21330051920178</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D26" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -6687,13 +6702,13 @@
         <v>21330051920179</v>
       </c>
       <c r="B27" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -6704,13 +6719,13 @@
         <v>21330051920180</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D28" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -6721,13 +6736,13 @@
         <v>21330051920181</v>
       </c>
       <c r="B29" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D29" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -6738,13 +6753,13 @@
         <v>21330051920182</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D30" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -6755,13 +6770,13 @@
         <v>21330051920183</v>
       </c>
       <c r="B31" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D31" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -6772,13 +6787,13 @@
         <v>21330051920184</v>
       </c>
       <c r="B32" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D32" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -6800,16 +6815,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -6826,13 +6841,13 @@
         <v>21330051920163</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -6849,19 +6864,19 @@
         <v>21330051920163</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6872,13 +6887,13 @@
         <v>21330051920171</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -6895,19 +6910,19 @@
         <v>21330051920171</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6918,13 +6933,13 @@
         <v>21330051920176</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D6" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -6941,19 +6956,19 @@
         <v>21330051920176</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6964,19 +6979,19 @@
         <v>21330051920156</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6987,19 +7002,19 @@
         <v>21330051920164</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E9" t="s">
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7010,13 +7025,13 @@
         <v>21330051920170</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -7033,13 +7048,13 @@
         <v>21330051920181</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D11" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>

--- a/grupos/4AEM - Estadisticos 20222.xlsx
+++ b/grupos/4AEM - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="87">
   <si>
     <t>Materia</t>
   </si>
@@ -189,18 +188,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
     <t>Torres Sánchez José Luis</t>
   </si>
   <si>
@@ -219,241 +218,76 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BAROJAS</t>
-  </si>
-  <si>
-    <t>CUAQUEHUA</t>
-  </si>
-  <si>
     <t>EVANGELISTA</t>
   </si>
   <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
-    <t>FERNANDEZ</t>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>LOYO</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>TERRAZAS</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>NERI</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>NIEVES</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>LOYO</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>MAYO</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>TERRAZAS</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>VIVAS</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>DIMAS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>NERI</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>AMECA</t>
-  </si>
-  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>SAMUEL</t>
-  </si>
-  <si>
-    <t>CRISTIAN ALEXIS</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>CARLOS DANIEL</t>
-  </si>
-  <si>
     <t>JUAN GERARDO</t>
   </si>
   <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>EVELIN MAYRIN</t>
-  </si>
-  <si>
-    <t>MARIO</t>
-  </si>
-  <si>
-    <t>FELIX RAYMUNDO</t>
-  </si>
-  <si>
-    <t>SAUL</t>
-  </si>
-  <si>
-    <t>CRISTIAN FERNANDO</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
   </si>
   <si>
     <t>DIEGO ARMANDO</t>
   </si>
   <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>LUIS OMAR</t>
-  </si>
-  <si>
-    <t>SALVADOR</t>
-  </si>
-  <si>
-    <t>CHARBEL</t>
-  </si>
-  <si>
-    <t>TAURINO</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>CHRISTIAN GABRIEL</t>
-  </si>
-  <si>
-    <t>JHOSUA LEVY</t>
-  </si>
-  <si>
     <t>CANDIDO</t>
   </si>
   <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>MANUEL</t>
-  </si>
-  <si>
     <t>MARIA REYNA</t>
   </si>
   <si>
     <t>ADALY</t>
-  </si>
-  <si>
-    <t>CHRISTOFER</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -506,11 +340,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -970,22 +805,22 @@
         <v>7</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -1015,13 +850,13 @@
         <v>6</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>8</v>
       </c>
       <c r="Z4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA4">
         <v>8</v>
@@ -1059,22 +894,22 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -1101,7 +936,7 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -1148,22 +983,22 @@
         <v>6</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -1193,19 +1028,19 @@
         <v>6</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y6">
         <v>8</v>
       </c>
       <c r="Z6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC6">
         <v>6</v>
@@ -1237,22 +1072,22 @@
         <v>7</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1282,7 +1117,7 @@
         <v>6</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1291,10 +1126,10 @@
         <v>6</v>
       </c>
       <c r="AA7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC7">
         <v>7</v>
@@ -1326,22 +1161,22 @@
         <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1371,7 +1206,7 @@
         <v>7</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y8">
         <v>8</v>
@@ -1380,10 +1215,10 @@
         <v>10</v>
       </c>
       <c r="AA8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC8">
         <v>8</v>
@@ -1415,22 +1250,22 @@
         <v>5</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1469,10 +1304,10 @@
         <v>5</v>
       </c>
       <c r="AA9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC9">
         <v>5</v>
@@ -1504,22 +1339,22 @@
         <v>6</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -1549,7 +1384,7 @@
         <v>5</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -1558,10 +1393,10 @@
         <v>6</v>
       </c>
       <c r="AA10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC10">
         <v>6</v>
@@ -1593,22 +1428,22 @@
         <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1647,10 +1482,10 @@
         <v>10</v>
       </c>
       <c r="AA11">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB11">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC11">
         <v>10</v>
@@ -1682,22 +1517,22 @@
         <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1771,22 +1606,22 @@
         <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1813,10 +1648,10 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -1860,22 +1695,22 @@
         <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -1902,7 +1737,7 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>9</v>
@@ -1911,13 +1746,13 @@
         <v>8</v>
       </c>
       <c r="Z14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC14">
         <v>7</v>
@@ -1949,22 +1784,22 @@
         <v>5</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -2038,22 +1873,22 @@
         <v>5</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -2080,22 +1915,22 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y16">
         <v>8</v>
       </c>
       <c r="Z16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC16">
         <v>5</v>
@@ -2127,22 +1962,22 @@
         <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -2178,13 +2013,13 @@
         <v>8</v>
       </c>
       <c r="Z17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC17">
         <v>6</v>
@@ -2216,22 +2051,22 @@
         <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -2261,7 +2096,7 @@
         <v>5</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>8</v>
@@ -2270,10 +2105,10 @@
         <v>7</v>
       </c>
       <c r="AA18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC18">
         <v>6</v>
@@ -2305,22 +2140,22 @@
         <v>6</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -2347,22 +2182,22 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>8</v>
       </c>
       <c r="Z19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC19">
         <v>6</v>
@@ -2394,22 +2229,22 @@
         <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2436,10 +2271,10 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>8</v>
@@ -2448,10 +2283,10 @@
         <v>10</v>
       </c>
       <c r="AA20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC20">
         <v>6</v>
@@ -2483,22 +2318,22 @@
         <v>5</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2525,7 +2360,7 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X21">
         <v>5</v>
@@ -2537,10 +2372,10 @@
         <v>5</v>
       </c>
       <c r="AA21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC21">
         <v>5</v>
@@ -2572,22 +2407,22 @@
         <v>5</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2623,13 +2458,13 @@
         <v>8</v>
       </c>
       <c r="Z22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC22">
         <v>5</v>
@@ -2661,22 +2496,22 @@
         <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -2703,16 +2538,16 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y23">
         <v>8</v>
       </c>
       <c r="Z23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA23">
         <v>8</v>
@@ -2750,22 +2585,22 @@
         <v>5</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -2792,10 +2627,10 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>8</v>
@@ -2839,22 +2674,22 @@
         <v>7</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -2884,7 +2719,7 @@
         <v>6</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y25">
         <v>8</v>
@@ -2928,22 +2763,22 @@
         <v>5</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -2973,7 +2808,7 @@
         <v>5</v>
       </c>
       <c r="X26">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y26">
         <v>8</v>
@@ -2982,10 +2817,10 @@
         <v>5</v>
       </c>
       <c r="AA26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC26">
         <v>5</v>
@@ -3017,22 +2852,22 @@
         <v>5</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
         <v>-1</v>
@@ -3062,13 +2897,13 @@
         <v>6</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y27">
         <v>8</v>
       </c>
       <c r="Z27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA27">
         <v>9</v>
@@ -3106,22 +2941,22 @@
         <v>8</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -3148,16 +2983,16 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X28">
+        <v>10</v>
+      </c>
+      <c r="Y28">
+        <v>8</v>
+      </c>
+      <c r="Z28">
         <v>9</v>
-      </c>
-      <c r="Y28">
-        <v>8</v>
-      </c>
-      <c r="Z28">
-        <v>7</v>
       </c>
       <c r="AA28">
         <v>9</v>
@@ -3195,22 +3030,22 @@
         <v>8</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -3249,10 +3084,10 @@
         <v>10</v>
       </c>
       <c r="AA29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC29">
         <v>8</v>
@@ -3284,22 +3119,22 @@
         <v>8</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -3326,7 +3161,7 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X30">
         <v>10</v>
@@ -3335,13 +3170,13 @@
         <v>8</v>
       </c>
       <c r="Z30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA30">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB30">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC30">
         <v>8</v>
@@ -3355,7 +3190,7 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D31">
         <v>8</v>
@@ -3373,22 +3208,22 @@
         <v>8</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K31">
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O31">
         <v>-1</v>
@@ -3415,22 +3250,22 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>8</v>
       </c>
       <c r="Z31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC31">
         <v>8</v>
@@ -3462,22 +3297,22 @@
         <v>7</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K32">
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O32">
         <v>-1</v>
@@ -3504,22 +3339,22 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y32">
         <v>8</v>
       </c>
       <c r="Z32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC32">
         <v>7</v>
@@ -3551,22 +3386,22 @@
         <v>8</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O33">
         <v>-1</v>
@@ -3602,13 +3437,13 @@
         <v>8</v>
       </c>
       <c r="Z33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA33">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB33">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC33">
         <v>8</v>
@@ -3640,22 +3475,22 @@
         <v>7</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O34">
         <v>-1</v>
@@ -3851,22 +3686,22 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -3919,22 +3754,22 @@
         <v>100</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -3987,22 +3822,22 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -4055,22 +3890,22 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -4123,22 +3958,22 @@
         <v>100</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -4203,10 +4038,10 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -4259,22 +4094,22 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -4327,22 +4162,22 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>103.3</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -4395,22 +4230,22 @@
         <v>83.3</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>103.3</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -4463,22 +4298,22 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -4531,22 +4366,22 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>103.3</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -4599,22 +4434,22 @@
         <v>76.7</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -4667,22 +4502,22 @@
         <v>76.7</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K16">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -4735,22 +4570,22 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>63.3</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -4803,22 +4638,22 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>103.3</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -4871,22 +4706,22 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>63.3</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>103.3</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -4939,22 +4774,22 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -5007,22 +4842,22 @@
         <v>80</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K21">
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>56.7</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -5075,22 +4910,22 @@
         <v>66.7</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>56.7</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -5143,22 +4978,22 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K23">
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>103.3</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -5211,22 +5046,22 @@
         <v>83.3</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K24">
         <v>0</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -5279,22 +5114,22 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -5347,22 +5182,22 @@
         <v>86.7</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K26">
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -5415,22 +5250,22 @@
         <v>86.7</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -5483,22 +5318,22 @@
         <v>100</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K28">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -5551,22 +5386,22 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>103.3</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -5619,22 +5454,22 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>63.3</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O30">
         <v>0</v>
@@ -5687,22 +5522,22 @@
         <v>100</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>63.3</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -5755,22 +5590,22 @@
         <v>100</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -5823,22 +5658,22 @@
         <v>100</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -5891,22 +5726,22 @@
         <v>100</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -5949,6 +5784,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -5985,7 +5822,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>
@@ -5994,30 +5831,30 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E2">
-        <v>12</v>
-      </c>
-      <c r="F2">
-        <v>61.29</v>
-      </c>
-      <c r="G2">
-        <v>38.71</v>
+        <v>14</v>
+      </c>
+      <c r="F2" s="2">
+        <v>54.8</v>
+      </c>
+      <c r="G2" s="2">
+        <v>45.2</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
@@ -6031,19 +5868,19 @@
       <c r="E3">
         <v>8</v>
       </c>
-      <c r="F3">
-        <v>74.19</v>
-      </c>
-      <c r="G3">
-        <v>25.81</v>
+      <c r="F3" s="2">
+        <v>74.2</v>
+      </c>
+      <c r="G3" s="2">
+        <v>25.8</v>
       </c>
       <c r="H3">
-        <v>6.1</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6063,11 +5900,11 @@
       <c r="E4">
         <v>8</v>
       </c>
-      <c r="F4">
-        <v>74.19</v>
-      </c>
-      <c r="G4">
-        <v>25.81</v>
+      <c r="F4" s="2">
+        <v>74.2</v>
+      </c>
+      <c r="G4" s="2">
+        <v>25.8</v>
       </c>
       <c r="H4">
         <v>6.8</v>
@@ -6075,13 +5912,13 @@
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
@@ -6090,24 +5927,24 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>80.65000000000001</v>
-      </c>
-      <c r="G5">
-        <v>19.35</v>
+        <v>7</v>
+      </c>
+      <c r="F5" s="2">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="G5" s="2">
+        <v>22.6</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6122,24 +5959,24 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>96.77</v>
-      </c>
-      <c r="G6">
-        <v>3.23</v>
+        <v>2</v>
+      </c>
+      <c r="F6" s="2">
+        <v>93.5</v>
+      </c>
+      <c r="G6" s="2">
+        <v>6.5</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6154,24 +5991,24 @@
         <v>31</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>96.77</v>
-      </c>
-      <c r="G7">
-        <v>3.23</v>
+        <v>2</v>
+      </c>
+      <c r="F7" s="2">
+        <v>93.5</v>
+      </c>
+      <c r="G7" s="2">
+        <v>6.5</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6191,10 +6028,10 @@
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8">
-        <v>100</v>
-      </c>
-      <c r="G8">
+      <c r="F8" s="2">
+        <v>100</v>
+      </c>
+      <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8">
@@ -6203,7 +6040,7 @@
       <c r="I8">
         <v>0</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6248,564 +6085,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E32"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>21330051920151</v>
-      </c>
-      <c r="B2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>21330051920152</v>
-      </c>
-      <c r="B3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>21330051920153</v>
-      </c>
-      <c r="B4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D4" t="s">
-        <v>116</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>21330051920154</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D5" t="s">
-        <v>117</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>21330051920155</v>
-      </c>
-      <c r="B6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>21330051920156</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>21330051920157</v>
-      </c>
-      <c r="B8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D8" t="s">
-        <v>120</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>21330051920158</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>101</v>
-      </c>
-      <c r="D9" t="s">
-        <v>121</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>21330051920159</v>
-      </c>
-      <c r="B10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D10" t="s">
-        <v>122</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>21330051920160</v>
-      </c>
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D11" t="s">
-        <v>123</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>21330051920161</v>
-      </c>
-      <c r="B12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" t="s">
-        <v>102</v>
-      </c>
-      <c r="D12" t="s">
-        <v>124</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>21330051920162</v>
-      </c>
-      <c r="B13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" t="s">
-        <v>125</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>21330051920163</v>
-      </c>
-      <c r="B14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" t="s">
-        <v>97</v>
-      </c>
-      <c r="D14" t="s">
-        <v>126</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>21330051920164</v>
-      </c>
-      <c r="B15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" t="s">
-        <v>103</v>
-      </c>
-      <c r="D15" t="s">
-        <v>127</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>21330051920165</v>
-      </c>
-      <c r="B16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" t="s">
-        <v>104</v>
-      </c>
-      <c r="D16" t="s">
-        <v>128</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>21330051920166</v>
-      </c>
-      <c r="B17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" t="s">
-        <v>105</v>
-      </c>
-      <c r="D17" t="s">
-        <v>129</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>21330051920167</v>
-      </c>
-      <c r="B18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" t="s">
-        <v>106</v>
-      </c>
-      <c r="D18" t="s">
-        <v>130</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>21330051920168</v>
-      </c>
-      <c r="B19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" t="s">
-        <v>131</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>21330051920169</v>
-      </c>
-      <c r="B20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" t="s">
-        <v>76</v>
-      </c>
-      <c r="D20" t="s">
-        <v>132</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>21330051920170</v>
-      </c>
-      <c r="B21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" t="s">
-        <v>93</v>
-      </c>
-      <c r="D21" t="s">
-        <v>133</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>21330051920171</v>
-      </c>
-      <c r="B22" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" t="s">
-        <v>83</v>
-      </c>
-      <c r="D22" t="s">
-        <v>134</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>21330051920173</v>
-      </c>
-      <c r="B23" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" t="s">
-        <v>107</v>
-      </c>
-      <c r="D23" t="s">
-        <v>135</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>21330051920175</v>
-      </c>
-      <c r="B24" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" t="s">
-        <v>108</v>
-      </c>
-      <c r="D24" t="s">
-        <v>136</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>21330051920176</v>
-      </c>
-      <c r="B25" t="s">
-        <v>87</v>
-      </c>
-      <c r="C25" t="s">
-        <v>109</v>
-      </c>
-      <c r="D25" t="s">
-        <v>137</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>21330051920178</v>
-      </c>
-      <c r="B26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" t="s">
-        <v>110</v>
-      </c>
-      <c r="D26" t="s">
-        <v>138</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>21330051920179</v>
-      </c>
-      <c r="B27" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" t="s">
-        <v>111</v>
-      </c>
-      <c r="D27" t="s">
-        <v>139</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>21330051920180</v>
-      </c>
-      <c r="B28" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" t="s">
-        <v>74</v>
-      </c>
-      <c r="D28" t="s">
-        <v>140</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>21330051920181</v>
-      </c>
-      <c r="B29" t="s">
-        <v>91</v>
-      </c>
-      <c r="C29" t="s">
-        <v>112</v>
-      </c>
-      <c r="D29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>21330051920182</v>
-      </c>
-      <c r="B30" t="s">
-        <v>92</v>
-      </c>
-      <c r="C30" t="s">
-        <v>83</v>
-      </c>
-      <c r="D30" t="s">
-        <v>142</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>21330051920183</v>
-      </c>
-      <c r="B31" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" t="s">
-        <v>113</v>
-      </c>
-      <c r="D31" t="s">
-        <v>129</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>21330051920184</v>
-      </c>
-      <c r="B32" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32" t="s">
-        <v>91</v>
-      </c>
-      <c r="D32" t="s">
-        <v>114</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6838,19 +6117,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920163</v>
+        <v>21330051920156</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>56</v>
@@ -6861,22 +6140,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920163</v>
+        <v>21330051920156</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6884,19 +6163,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920171</v>
+        <v>21330051920165</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>56</v>
@@ -6907,22 +6186,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920171</v>
+        <v>21330051920165</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6930,19 +6209,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920176</v>
+        <v>21330051920166</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>137</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
         <v>56</v>
@@ -6953,22 +6232,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920176</v>
+        <v>21330051920166</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>137</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6976,22 +6255,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920156</v>
+        <v>21330051920164</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6999,22 +6278,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920164</v>
+        <v>21330051920176</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7022,19 +6301,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920170</v>
+        <v>21330051920180</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>133</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
         <v>56</v>
@@ -7048,16 +6327,16 @@
         <v>21330051920181</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>141</v>
+        <v>86</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
         <v>56</v>

--- a/grupos/4AEM - Estadisticos 20222.xlsx
+++ b/grupos/4AEM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="93">
   <si>
     <t>Materia</t>
   </si>
@@ -194,15 +194,15 @@
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Torres Sánchez José Luis</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Torres Sánchez José Luis</t>
-  </si>
-  <si>
     <t>Medina Tolentino Elio</t>
   </si>
   <si>
@@ -221,18 +221,24 @@
     <t>EVANGELISTA</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>LORENZO</t>
   </si>
   <si>
     <t>MACARIO</t>
   </si>
   <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>LOYO</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
     <t>TERRAZAS</t>
   </si>
   <si>
@@ -242,18 +248,24 @@
     <t>DE LA LUZ</t>
   </si>
   <si>
+    <t>MONGE</t>
+  </si>
+  <si>
     <t>ROSETE</t>
   </si>
   <si>
     <t>NERI</t>
   </si>
   <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -263,16 +275,22 @@
     <t>JUAN GERARDO</t>
   </si>
   <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
     <t>ROBERTO</t>
   </si>
   <si>
     <t>MARIA JOSE</t>
   </si>
   <si>
+    <t>YAHIR</t>
+  </si>
+  <si>
+    <t>JHOSUA LEVY</t>
+  </si>
+  <si>
     <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>CANDIDO</t>
   </si>
   <si>
     <t>MARIA REYNA</t>
@@ -823,7 +841,7 @@
         <v>7</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -865,7 +883,7 @@
         <v>8</v>
       </c>
       <c r="AC4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -912,7 +930,7 @@
         <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1001,7 +1019,7 @@
         <v>5</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1043,7 +1061,7 @@
         <v>6</v>
       </c>
       <c r="AC6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1090,7 +1108,7 @@
         <v>5</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1132,7 +1150,7 @@
         <v>7</v>
       </c>
       <c r="AC7">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1179,7 +1197,7 @@
         <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1221,7 +1239,7 @@
         <v>10</v>
       </c>
       <c r="AC8">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1268,7 +1286,7 @@
         <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1357,7 +1375,7 @@
         <v>5</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1399,7 +1417,7 @@
         <v>7</v>
       </c>
       <c r="AC10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1446,7 +1464,7 @@
         <v>5</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1624,7 +1642,7 @@
         <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1713,7 +1731,7 @@
         <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1755,7 +1773,7 @@
         <v>9</v>
       </c>
       <c r="AC14">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1802,7 +1820,7 @@
         <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1844,7 +1862,7 @@
         <v>5</v>
       </c>
       <c r="AC15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1891,7 +1909,7 @@
         <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1933,7 +1951,7 @@
         <v>6</v>
       </c>
       <c r="AC16">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2247,7 +2265,7 @@
         <v>5</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2289,7 +2307,7 @@
         <v>6</v>
       </c>
       <c r="AC20">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2336,7 +2354,7 @@
         <v>5</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2378,7 +2396,7 @@
         <v>5</v>
       </c>
       <c r="AC21">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2514,7 +2532,7 @@
         <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2556,7 +2574,7 @@
         <v>8</v>
       </c>
       <c r="AC23">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2603,7 +2621,7 @@
         <v>7</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2645,7 +2663,7 @@
         <v>7</v>
       </c>
       <c r="AC24">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2692,7 +2710,7 @@
         <v>7</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2734,7 +2752,7 @@
         <v>8</v>
       </c>
       <c r="AC25">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2781,7 +2799,7 @@
         <v>5</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2823,7 +2841,7 @@
         <v>7</v>
       </c>
       <c r="AC26">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2870,7 +2888,7 @@
         <v>9</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2912,7 +2930,7 @@
         <v>9</v>
       </c>
       <c r="AC27">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -2959,7 +2977,7 @@
         <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3001,7 +3019,7 @@
         <v>9</v>
       </c>
       <c r="AC28">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3048,7 +3066,7 @@
         <v>9</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3090,7 +3108,7 @@
         <v>9</v>
       </c>
       <c r="AC29">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3137,7 +3155,7 @@
         <v>5</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3179,7 +3197,7 @@
         <v>7</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3226,7 +3244,7 @@
         <v>5</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3268,7 +3286,7 @@
         <v>7</v>
       </c>
       <c r="AC31">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3315,7 +3333,7 @@
         <v>6</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3357,7 +3375,7 @@
         <v>7</v>
       </c>
       <c r="AC32">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3404,7 +3422,7 @@
         <v>5</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3446,7 +3464,7 @@
         <v>7</v>
       </c>
       <c r="AC33">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3493,7 +3511,7 @@
         <v>7</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3535,7 +3553,7 @@
         <v>8</v>
       </c>
       <c r="AC34">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3704,7 +3722,7 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -3772,7 +3790,7 @@
         <v>100</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -3840,7 +3858,7 @@
         <v>80</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -3908,7 +3926,7 @@
         <v>73.3</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -3976,7 +3994,7 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -4112,7 +4130,7 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -4180,7 +4198,7 @@
         <v>103.3</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -4248,7 +4266,7 @@
         <v>103.3</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -4316,7 +4334,7 @@
         <v>106.7</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -4384,7 +4402,7 @@
         <v>103.3</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -4452,7 +4470,7 @@
         <v>93.3</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -4520,7 +4538,7 @@
         <v>90</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -4588,7 +4606,7 @@
         <v>100</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -4656,7 +4674,7 @@
         <v>103.3</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -4724,7 +4742,7 @@
         <v>103.3</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -4792,7 +4810,7 @@
         <v>93.3</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -4860,7 +4878,7 @@
         <v>76.7</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -4928,7 +4946,7 @@
         <v>76.7</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -4996,7 +5014,7 @@
         <v>103.3</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -5064,7 +5082,7 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -5132,7 +5150,7 @@
         <v>100</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -5200,7 +5218,7 @@
         <v>96.7</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -5268,7 +5286,7 @@
         <v>100</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -5336,7 +5354,7 @@
         <v>100</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -5404,7 +5422,7 @@
         <v>103.3</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -5472,7 +5490,7 @@
         <v>90</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P30">
         <v>0</v>
@@ -5540,7 +5558,7 @@
         <v>96.7</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -5608,7 +5626,7 @@
         <v>96.7</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P32">
         <v>0</v>
@@ -5676,7 +5694,7 @@
         <v>100</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -5744,7 +5762,7 @@
         <v>100</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P34">
         <v>0</v>
@@ -5886,7 +5904,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -5895,19 +5913,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>74.2</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>25.8</v>
+        <v>22.6</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5918,7 +5936,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
@@ -5927,19 +5945,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>77.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="G5" s="2">
-        <v>22.6</v>
+        <v>6.5</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5950,7 +5968,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>60</v>
@@ -5971,7 +5989,7 @@
         <v>6.5</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5985,7 +6003,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7">
         <v>31</v>
@@ -6085,7 +6103,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6123,10 +6141,10 @@
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6146,10 +6164,10 @@
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -6163,16 +6181,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920165</v>
+        <v>21330051920163</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -6186,16 +6204,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920165</v>
+        <v>21330051920163</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -6209,16 +6227,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920166</v>
+        <v>21330051920165</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -6232,22 +6250,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920166</v>
+        <v>21330051920165</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6255,16 +6273,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920164</v>
+        <v>21330051920166</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -6278,19 +6296,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920176</v>
+        <v>21330051920166</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
         <v>58</v>
@@ -6301,16 +6319,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920180</v>
+        <v>21330051920171</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -6324,24 +6342,139 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920181</v>
+        <v>21330051920171</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
         <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920175</v>
+      </c>
+      <c r="B12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" t="s">
         <v>56</v>
       </c>
-      <c r="G11">
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920175</v>
+      </c>
+      <c r="B13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920164</v>
+      </c>
+      <c r="B14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>56</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920180</v>
+      </c>
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" t="s">
+        <v>56</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21330051920181</v>
+      </c>
+      <c r="B16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4AEM - Estadisticos 20222.xlsx
+++ b/grupos/4AEM - Estadisticos 20222.xlsx
@@ -829,7 +829,7 @@
         <v>5</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>10</v>
@@ -918,7 +918,7 @@
         <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -1007,7 +1007,7 @@
         <v>5</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>8</v>
@@ -1096,7 +1096,7 @@
         <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>6</v>
@@ -1185,7 +1185,7 @@
         <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <v>10</v>
@@ -1274,7 +1274,7 @@
         <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
         <v>5</v>
@@ -1363,7 +1363,7 @@
         <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>6</v>
@@ -1452,7 +1452,7 @@
         <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
         <v>10</v>
@@ -1541,7 +1541,7 @@
         <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
         <v>6</v>
@@ -1583,7 +1583,7 @@
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z12">
         <v>5</v>
@@ -1630,7 +1630,7 @@
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>10</v>
@@ -1672,7 +1672,7 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z13">
         <v>10</v>
@@ -1719,7 +1719,7 @@
         <v>9</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
         <v>10</v>
@@ -1808,7 +1808,7 @@
         <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>5</v>
@@ -1897,7 +1897,7 @@
         <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
         <v>7</v>
@@ -1986,7 +1986,7 @@
         <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>9</v>
@@ -2028,7 +2028,7 @@
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z17">
         <v>7</v>
@@ -2075,7 +2075,7 @@
         <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>7</v>
@@ -2164,7 +2164,7 @@
         <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>5</v>
@@ -2253,7 +2253,7 @@
         <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
         <v>10</v>
@@ -2342,7 +2342,7 @@
         <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>5</v>
@@ -2431,7 +2431,7 @@
         <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
         <v>9</v>
@@ -2520,7 +2520,7 @@
         <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
         <v>9</v>
@@ -2609,7 +2609,7 @@
         <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
         <v>6</v>
@@ -2698,7 +2698,7 @@
         <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L25">
         <v>10</v>
@@ -2787,7 +2787,7 @@
         <v>5</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
         <v>6</v>
@@ -2876,7 +2876,7 @@
         <v>5</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L27">
         <v>8</v>
@@ -2965,7 +2965,7 @@
         <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
         <v>10</v>
@@ -3054,7 +3054,7 @@
         <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L29">
         <v>10</v>
@@ -3143,7 +3143,7 @@
         <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
         <v>8</v>
@@ -3232,7 +3232,7 @@
         <v>6</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
         <v>7</v>
@@ -3321,7 +3321,7 @@
         <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L32">
         <v>8</v>
@@ -3410,7 +3410,7 @@
         <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L33">
         <v>10</v>
@@ -3499,7 +3499,7 @@
         <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L34">
         <v>10</v>
@@ -3710,7 +3710,7 @@
         <v>100</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L4">
         <v>106.7</v>
@@ -3778,7 +3778,7 @@
         <v>100</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L5">
         <v>106.7</v>
@@ -3846,7 +3846,7 @@
         <v>100</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L6">
         <v>106.7</v>
@@ -3914,7 +3914,7 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L7">
         <v>106.7</v>
@@ -3982,7 +3982,7 @@
         <v>100</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8">
         <v>106.7</v>
@@ -4050,7 +4050,7 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -4118,7 +4118,7 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10">
         <v>106.7</v>
@@ -4186,7 +4186,7 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L11">
         <v>106.7</v>
@@ -4254,7 +4254,7 @@
         <v>100</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L12">
         <v>106.7</v>
@@ -4322,7 +4322,7 @@
         <v>100</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L13">
         <v>106.7</v>
@@ -4390,7 +4390,7 @@
         <v>100</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14">
         <v>106.7</v>
@@ -4458,7 +4458,7 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15">
         <v>106.7</v>
@@ -4526,7 +4526,7 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L16">
         <v>106.7</v>
@@ -4594,7 +4594,7 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L17">
         <v>106.7</v>
@@ -4662,7 +4662,7 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L18">
         <v>106.7</v>
@@ -4730,7 +4730,7 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L19">
         <v>106.7</v>
@@ -4798,7 +4798,7 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20">
         <v>106.7</v>
@@ -4866,7 +4866,7 @@
         <v>100</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L21">
         <v>106.7</v>
@@ -4934,7 +4934,7 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22">
         <v>106.7</v>
@@ -5002,7 +5002,7 @@
         <v>100</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L23">
         <v>106.7</v>
@@ -5070,7 +5070,7 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24">
         <v>106.7</v>
@@ -5138,7 +5138,7 @@
         <v>100</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L25">
         <v>106.7</v>
@@ -5206,7 +5206,7 @@
         <v>100</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L26">
         <v>106.7</v>
@@ -5274,7 +5274,7 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L27">
         <v>106.7</v>
@@ -5342,7 +5342,7 @@
         <v>100</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L28">
         <v>106.7</v>
@@ -5410,7 +5410,7 @@
         <v>100</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29">
         <v>106.7</v>
@@ -5478,7 +5478,7 @@
         <v>100</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30">
         <v>106.7</v>
@@ -5546,7 +5546,7 @@
         <v>100</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L31">
         <v>106.7</v>
@@ -5614,7 +5614,7 @@
         <v>100</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L32">
         <v>106.7</v>
@@ -5682,7 +5682,7 @@
         <v>100</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33">
         <v>106.7</v>
@@ -5750,7 +5750,7 @@
         <v>100</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L34">
         <v>106.7</v>
@@ -6053,7 +6053,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I8">
         <v>0</v>

--- a/grupos/4AEM - Estadisticos 20222.xlsx
+++ b/grupos/4AEM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="90">
   <si>
     <t>Materia</t>
   </si>
@@ -197,12 +197,12 @@
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Torres Sánchez José Luis</t>
   </si>
   <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
     <t>Medina Tolentino Elio</t>
   </si>
   <si>
@@ -224,7 +224,7 @@
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>LORENZO</t>
+    <t>LOYO</t>
   </si>
   <si>
     <t>MACARIO</t>
@@ -236,9 +236,6 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>LOYO</t>
-  </si>
-  <si>
     <t>TERRAZAS</t>
   </si>
   <si>
@@ -251,7 +248,7 @@
     <t>MONGE</t>
   </si>
   <si>
-    <t>ROSETE</t>
+    <t>ROMERO</t>
   </si>
   <si>
     <t>NERI</t>
@@ -263,9 +260,6 @@
     <t>SOLIS</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -278,7 +272,7 @@
     <t>MIGUEL</t>
   </si>
   <si>
-    <t>ROBERTO</t>
+    <t>DIEGO ARMANDO</t>
   </si>
   <si>
     <t>MARIA JOSE</t>
@@ -288,9 +282,6 @@
   </si>
   <si>
     <t>JHOSUA LEVY</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
   </si>
   <si>
     <t>MARIA REYNA</t>
@@ -1553,7 +1544,7 @@
         <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1595,7 +1586,7 @@
         <v>8</v>
       </c>
       <c r="AC12">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1998,7 +1989,7 @@
         <v>5</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2040,7 +2031,7 @@
         <v>6</v>
       </c>
       <c r="AC17">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2087,7 +2078,7 @@
         <v>5</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2129,7 +2120,7 @@
         <v>6</v>
       </c>
       <c r="AC18">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2176,7 +2167,7 @@
         <v>5</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2218,7 +2209,7 @@
         <v>6</v>
       </c>
       <c r="AC19">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2443,7 +2434,7 @@
         <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -5936,7 +5927,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
@@ -5945,19 +5936,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2">
-        <v>93.5</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>6.5</v>
+        <v>16.1</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5968,7 +5959,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>60</v>
@@ -5989,7 +5980,7 @@
         <v>6.5</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6003,7 +5994,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C7">
         <v>31</v>
@@ -6103,7 +6094,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6141,10 +6132,10 @@
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6164,10 +6155,10 @@
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -6187,10 +6178,10 @@
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -6210,10 +6201,10 @@
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -6227,16 +6218,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920165</v>
+        <v>21330051920164</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -6250,22 +6241,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920165</v>
+        <v>21330051920164</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6279,10 +6270,10 @@
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -6302,10 +6293,10 @@
         <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -6325,10 +6316,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -6348,10 +6339,10 @@
         <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -6371,10 +6362,10 @@
         <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
@@ -6394,10 +6385,10 @@
         <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -6411,16 +6402,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920164</v>
+        <v>21330051920180</v>
       </c>
       <c r="B14" t="s">
         <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -6434,16 +6425,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920180</v>
+        <v>21330051920181</v>
       </c>
       <c r="B15" t="s">
         <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E15" t="s">
         <v>5</v>
@@ -6452,29 +6443,6 @@
         <v>56</v>
       </c>
       <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920181</v>
-      </c>
-      <c r="B16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" t="s">
-        <v>83</v>
-      </c>
-      <c r="D16" t="s">
-        <v>92</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>56</v>
-      </c>
-      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4AEM - Estadisticos 20222.xlsx
+++ b/grupos/4AEM - Estadisticos 20222.xlsx
@@ -3683,19 +3683,19 @@
         <v>100</v>
       </c>
       <c r="E4">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F4">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>103.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H4">
         <v>100</v>
       </c>
       <c r="I4">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J4">
         <v>100</v>
@@ -3704,37 +3704,37 @@
         <v>100</v>
       </c>
       <c r="L4">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M4">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="N4">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O4">
         <v>100</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -3751,19 +3751,19 @@
         <v>100</v>
       </c>
       <c r="E5">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F5">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>106.7</v>
+        <v>97</v>
       </c>
       <c r="H5">
         <v>100</v>
       </c>
       <c r="I5">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J5">
         <v>100</v>
@@ -3772,37 +3772,37 @@
         <v>100</v>
       </c>
       <c r="L5">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M5">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="N5">
-        <v>100</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -3819,19 +3819,19 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F6">
-        <v>80</v>
+        <v>92.3</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H6">
         <v>100</v>
       </c>
       <c r="I6">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -3840,37 +3840,37 @@
         <v>100</v>
       </c>
       <c r="L6">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M6">
-        <v>60</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="N6">
-        <v>80</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="O6">
         <v>100</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -3887,58 +3887,58 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F7">
-        <v>80</v>
+        <v>92.3</v>
       </c>
       <c r="G7">
-        <v>106.7</v>
+        <v>97</v>
       </c>
       <c r="H7">
         <v>100</v>
       </c>
       <c r="I7">
+        <v>90</v>
+      </c>
+      <c r="J7">
         <v>95</v>
       </c>
-      <c r="J7">
-        <v>100</v>
-      </c>
       <c r="K7">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="L7">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M7">
-        <v>70</v>
+        <v>88.2</v>
       </c>
       <c r="N7">
-        <v>73.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="O7">
         <v>100</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>88.2</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -3955,19 +3955,19 @@
         <v>100</v>
       </c>
       <c r="E8">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F8">
-        <v>83.3</v>
+        <v>96.2</v>
       </c>
       <c r="G8">
-        <v>103.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H8">
         <v>100</v>
       </c>
       <c r="I8">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J8">
         <v>100</v>
@@ -3976,37 +3976,37 @@
         <v>100</v>
       </c>
       <c r="L8">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M8">
-        <v>83.3</v>
+        <v>98</v>
       </c>
       <c r="N8">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O8">
         <v>100</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -4023,58 +4023,58 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F9">
-        <v>80</v>
+        <v>92.3</v>
       </c>
       <c r="G9">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H9">
         <v>76.7</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M9">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="N9">
-        <v>33.3</v>
+        <v>66.2</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>38.3</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>66.2</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -4091,58 +4091,58 @@
         <v>100</v>
       </c>
       <c r="E10">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F10">
-        <v>80</v>
+        <v>92.3</v>
       </c>
       <c r="G10">
-        <v>106.7</v>
+        <v>97</v>
       </c>
       <c r="H10">
         <v>100</v>
       </c>
       <c r="I10">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J10">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="K10">
         <v>100</v>
       </c>
       <c r="L10">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M10">
-        <v>73.3</v>
+        <v>90.2</v>
       </c>
       <c r="N10">
-        <v>100</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O10">
         <v>100</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>90.2</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -4159,19 +4159,19 @@
         <v>100</v>
       </c>
       <c r="E11">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F11">
-        <v>83.3</v>
+        <v>96.2</v>
       </c>
       <c r="G11">
-        <v>103.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H11">
         <v>100</v>
       </c>
       <c r="I11">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J11">
         <v>100</v>
@@ -4180,37 +4180,37 @@
         <v>100</v>
       </c>
       <c r="L11">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M11">
-        <v>80</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="N11">
-        <v>103.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O11">
         <v>100</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -4227,58 +4227,58 @@
         <v>35</v>
       </c>
       <c r="E12">
-        <v>86.7</v>
+        <v>81.3</v>
       </c>
       <c r="F12">
-        <v>83.3</v>
+        <v>96.2</v>
       </c>
       <c r="G12">
-        <v>103.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H12">
         <v>83.3</v>
       </c>
       <c r="I12">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="J12">
-        <v>100</v>
+        <v>82.5</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>67.5</v>
       </c>
       <c r="L12">
-        <v>106.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="M12">
-        <v>80</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="N12">
-        <v>103.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O12">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -4295,13 +4295,13 @@
         <v>100</v>
       </c>
       <c r="E13">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F13">
-        <v>80</v>
+        <v>92.3</v>
       </c>
       <c r="G13">
-        <v>106.7</v>
+        <v>97</v>
       </c>
       <c r="H13">
         <v>100</v>
@@ -4310,43 +4310,43 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="K13">
         <v>100</v>
       </c>
       <c r="L13">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M13">
-        <v>83.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="N13">
-        <v>106.7</v>
+        <v>98.5</v>
       </c>
       <c r="O13">
         <v>100</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>98.5</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -4363,13 +4363,13 @@
         <v>100</v>
       </c>
       <c r="E14">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F14">
-        <v>80</v>
+        <v>92.3</v>
       </c>
       <c r="G14">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H14">
         <v>100</v>
@@ -4384,37 +4384,37 @@
         <v>100</v>
       </c>
       <c r="L14">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M14">
-        <v>83.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="N14">
-        <v>103.3</v>
+        <v>93.8</v>
       </c>
       <c r="O14">
         <v>100</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -4431,58 +4431,58 @@
         <v>15</v>
       </c>
       <c r="E15">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F15">
-        <v>76.7</v>
+        <v>88.5</v>
       </c>
       <c r="G15">
-        <v>93.3</v>
+        <v>84.8</v>
       </c>
       <c r="H15">
         <v>76.7</v>
       </c>
       <c r="I15">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="J15">
-        <v>100</v>
+        <v>82.5</v>
       </c>
       <c r="K15">
-        <v>100</v>
+        <v>57.5</v>
       </c>
       <c r="L15">
-        <v>106.7</v>
+        <v>87.5</v>
       </c>
       <c r="M15">
-        <v>73.3</v>
+        <v>88.2</v>
       </c>
       <c r="N15">
-        <v>93.3</v>
+        <v>86.2</v>
       </c>
       <c r="O15">
-        <v>100</v>
+        <v>88.3</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>57.5</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>88.2</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>86.2</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -4499,58 +4499,58 @@
         <v>45</v>
       </c>
       <c r="E16">
-        <v>86.7</v>
+        <v>81.3</v>
       </c>
       <c r="F16">
-        <v>76.7</v>
+        <v>88.5</v>
       </c>
       <c r="G16">
-        <v>106.7</v>
+        <v>97</v>
       </c>
       <c r="H16">
         <v>76.7</v>
       </c>
       <c r="I16">
-        <v>85</v>
+        <v>82.5</v>
       </c>
       <c r="J16">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>72.5</v>
       </c>
       <c r="L16">
-        <v>106.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="M16">
-        <v>70</v>
+        <v>86.3</v>
       </c>
       <c r="N16">
-        <v>90</v>
+        <v>90.8</v>
       </c>
       <c r="O16">
-        <v>100</v>
+        <v>88.3</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>72.5</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>86.3</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>90.8</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -4567,58 +4567,58 @@
         <v>55</v>
       </c>
       <c r="E17">
-        <v>86.7</v>
+        <v>81.3</v>
       </c>
       <c r="F17">
-        <v>76.7</v>
+        <v>88.5</v>
       </c>
       <c r="G17">
-        <v>106.7</v>
+        <v>97</v>
       </c>
       <c r="H17">
         <v>100</v>
       </c>
       <c r="I17">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="J17">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="K17">
-        <v>100</v>
+        <v>77.5</v>
       </c>
       <c r="L17">
-        <v>106.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="M17">
-        <v>63.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="N17">
-        <v>100</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O17">
         <v>100</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -4635,13 +4635,13 @@
         <v>100</v>
       </c>
       <c r="E18">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F18">
-        <v>80</v>
+        <v>92.3</v>
       </c>
       <c r="G18">
-        <v>103.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H18">
         <v>100</v>
@@ -4656,37 +4656,37 @@
         <v>100</v>
       </c>
       <c r="L18">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M18">
-        <v>70</v>
+        <v>88.2</v>
       </c>
       <c r="N18">
-        <v>103.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O18">
         <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>88.2</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -4703,58 +4703,58 @@
         <v>30</v>
       </c>
       <c r="E19">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F19">
-        <v>80</v>
+        <v>92.3</v>
       </c>
       <c r="G19">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H19">
         <v>100</v>
       </c>
       <c r="I19">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="J19">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="K19">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="L19">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M19">
-        <v>63.3</v>
+        <v>84.3</v>
       </c>
       <c r="N19">
-        <v>103.3</v>
+        <v>93.8</v>
       </c>
       <c r="O19">
         <v>100</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>84.3</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -4771,19 +4771,19 @@
         <v>100</v>
       </c>
       <c r="E20">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F20">
-        <v>80</v>
+        <v>92.3</v>
       </c>
       <c r="G20">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H20">
         <v>100</v>
       </c>
       <c r="I20">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J20">
         <v>100</v>
@@ -4792,37 +4792,37 @@
         <v>100</v>
       </c>
       <c r="L20">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M20">
-        <v>70</v>
+        <v>88.2</v>
       </c>
       <c r="N20">
-        <v>93.3</v>
+        <v>89.2</v>
       </c>
       <c r="O20">
         <v>100</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>88.2</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>89.2</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -4839,58 +4839,58 @@
         <v>40</v>
       </c>
       <c r="E21">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F21">
-        <v>76.7</v>
+        <v>88.5</v>
       </c>
       <c r="G21">
-        <v>103.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H21">
         <v>80</v>
       </c>
       <c r="I21">
-        <v>75</v>
+        <v>82.5</v>
       </c>
       <c r="J21">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K21">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="L21">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M21">
-        <v>56.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="N21">
-        <v>76.7</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="O21">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -4907,58 +4907,58 @@
         <v>5</v>
       </c>
       <c r="E22">
-        <v>86.7</v>
+        <v>81.3</v>
       </c>
       <c r="F22">
-        <v>76.7</v>
+        <v>88.5</v>
       </c>
       <c r="G22">
-        <v>106.7</v>
+        <v>97</v>
       </c>
       <c r="H22">
         <v>66.7</v>
       </c>
       <c r="I22">
-        <v>75</v>
+        <v>82.5</v>
       </c>
       <c r="J22">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>52.5</v>
       </c>
       <c r="L22">
-        <v>106.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="M22">
-        <v>56.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="N22">
-        <v>76.7</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="O22">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>52.5</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -4975,19 +4975,19 @@
         <v>100</v>
       </c>
       <c r="E23">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F23">
-        <v>83.3</v>
+        <v>96.2</v>
       </c>
       <c r="G23">
-        <v>106.7</v>
+        <v>97</v>
       </c>
       <c r="H23">
         <v>100</v>
       </c>
       <c r="I23">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J23">
         <v>100</v>
@@ -4996,37 +4996,37 @@
         <v>100</v>
       </c>
       <c r="L23">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M23">
-        <v>83.3</v>
+        <v>98</v>
       </c>
       <c r="N23">
-        <v>103.3</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O23">
         <v>100</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -5043,58 +5043,58 @@
         <v>100</v>
       </c>
       <c r="E24">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F24">
-        <v>80</v>
+        <v>92.3</v>
       </c>
       <c r="G24">
-        <v>103.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H24">
         <v>83.3</v>
       </c>
       <c r="I24">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="J24">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K24">
         <v>100</v>
       </c>
       <c r="L24">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M24">
-        <v>80</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="N24">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O24">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -5111,13 +5111,13 @@
         <v>100</v>
       </c>
       <c r="E25">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F25">
-        <v>83.3</v>
+        <v>96.2</v>
       </c>
       <c r="G25">
-        <v>106.7</v>
+        <v>97</v>
       </c>
       <c r="H25">
         <v>100</v>
@@ -5132,37 +5132,37 @@
         <v>100</v>
       </c>
       <c r="L25">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M25">
-        <v>80</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="N25">
-        <v>100</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O25">
         <v>100</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -5179,19 +5179,19 @@
         <v>100</v>
       </c>
       <c r="E26">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F26">
-        <v>80</v>
+        <v>92.3</v>
       </c>
       <c r="G26">
-        <v>103.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H26">
         <v>86.7</v>
       </c>
       <c r="I26">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J26">
         <v>100</v>
@@ -5200,37 +5200,37 @@
         <v>100</v>
       </c>
       <c r="L26">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M26">
-        <v>76.7</v>
+        <v>92.2</v>
       </c>
       <c r="N26">
-        <v>96.7</v>
+        <v>92.3</v>
       </c>
       <c r="O26">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>92.2</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>92.3</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -5247,58 +5247,58 @@
         <v>55</v>
       </c>
       <c r="E27">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F27">
-        <v>80</v>
+        <v>92.3</v>
       </c>
       <c r="G27">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H27">
         <v>86.7</v>
       </c>
       <c r="I27">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="J27">
         <v>100</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>77.5</v>
       </c>
       <c r="L27">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M27">
-        <v>80</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="N27">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="O27">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>92.3</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -5315,13 +5315,13 @@
         <v>100</v>
       </c>
       <c r="E28">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F28">
-        <v>83.3</v>
+        <v>96.2</v>
       </c>
       <c r="G28">
-        <v>106.7</v>
+        <v>97</v>
       </c>
       <c r="H28">
         <v>100</v>
@@ -5336,37 +5336,37 @@
         <v>100</v>
       </c>
       <c r="L28">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M28">
-        <v>80</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="N28">
-        <v>100</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O28">
         <v>100</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -5383,13 +5383,13 @@
         <v>100</v>
       </c>
       <c r="E29">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F29">
-        <v>80</v>
+        <v>92.3</v>
       </c>
       <c r="G29">
-        <v>103.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H29">
         <v>100</v>
@@ -5404,37 +5404,37 @@
         <v>100</v>
       </c>
       <c r="L29">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M29">
-        <v>80</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="N29">
-        <v>103.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O29">
         <v>100</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -5451,19 +5451,19 @@
         <v>100</v>
       </c>
       <c r="E30">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F30">
-        <v>83.3</v>
+        <v>96.2</v>
       </c>
       <c r="G30">
-        <v>103.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H30">
         <v>100</v>
       </c>
       <c r="I30">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J30">
         <v>100</v>
@@ -5472,37 +5472,37 @@
         <v>100</v>
       </c>
       <c r="L30">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M30">
-        <v>63.3</v>
+        <v>86.3</v>
       </c>
       <c r="N30">
-        <v>90</v>
+        <v>89.2</v>
       </c>
       <c r="O30">
         <v>100</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>86.3</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>89.2</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -5519,58 +5519,58 @@
         <v>100</v>
       </c>
       <c r="E31">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F31">
-        <v>80</v>
+        <v>92.3</v>
       </c>
       <c r="G31">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H31">
         <v>100</v>
       </c>
       <c r="I31">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J31">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="K31">
         <v>100</v>
       </c>
       <c r="L31">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M31">
-        <v>63.3</v>
+        <v>84.3</v>
       </c>
       <c r="N31">
-        <v>96.7</v>
+        <v>90.8</v>
       </c>
       <c r="O31">
         <v>100</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>84.3</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>90.8</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -5587,13 +5587,13 @@
         <v>100</v>
       </c>
       <c r="E32">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F32">
-        <v>76.7</v>
+        <v>88.5</v>
       </c>
       <c r="G32">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H32">
         <v>100</v>
@@ -5608,37 +5608,37 @@
         <v>100</v>
       </c>
       <c r="L32">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M32">
-        <v>76.7</v>
+        <v>90.2</v>
       </c>
       <c r="N32">
-        <v>96.7</v>
+        <v>90.8</v>
       </c>
       <c r="O32">
         <v>100</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>90.2</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>90.8</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -5655,19 +5655,19 @@
         <v>100</v>
       </c>
       <c r="E33">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F33">
-        <v>83.3</v>
+        <v>96.2</v>
       </c>
       <c r="G33">
-        <v>103.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H33">
         <v>100</v>
       </c>
       <c r="I33">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J33">
         <v>100</v>
@@ -5676,37 +5676,37 @@
         <v>100</v>
       </c>
       <c r="L33">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M33">
-        <v>80</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="N33">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O33">
         <v>100</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -5723,13 +5723,13 @@
         <v>100</v>
       </c>
       <c r="E34">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="F34">
-        <v>80</v>
+        <v>92.3</v>
       </c>
       <c r="G34">
-        <v>106.7</v>
+        <v>97</v>
       </c>
       <c r="H34">
         <v>100</v>
@@ -5744,37 +5744,37 @@
         <v>100</v>
       </c>
       <c r="L34">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="M34">
-        <v>80</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="N34">
-        <v>100</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O34">
         <v>100</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4AEM - Estadisticos 20222.xlsx
+++ b/grupos/4AEM - Estadisticos 20222.xlsx
@@ -3710,7 +3710,7 @@
         <v>98</v>
       </c>
       <c r="N4">
-        <v>93.8</v>
+        <v>95.3</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -3731,7 +3731,7 @@
         <v>98</v>
       </c>
       <c r="U4">
-        <v>93.8</v>
+        <v>95.3</v>
       </c>
       <c r="V4">
         <v>100</v>
@@ -3778,7 +3778,7 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>95.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O5">
         <v>100</v>
@@ -3799,7 +3799,7 @@
         <v>100</v>
       </c>
       <c r="U5">
-        <v>95.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -3846,7 +3846,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="N6">
-        <v>83.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="O6">
         <v>100</v>
@@ -3867,7 +3867,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="U6">
-        <v>83.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="V6">
         <v>100</v>
@@ -3914,7 +3914,7 @@
         <v>88.2</v>
       </c>
       <c r="N7">
-        <v>83.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="O7">
         <v>100</v>
@@ -3935,7 +3935,7 @@
         <v>88.2</v>
       </c>
       <c r="U7">
-        <v>83.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="V7">
         <v>100</v>
@@ -3982,7 +3982,7 @@
         <v>98</v>
       </c>
       <c r="N8">
-        <v>93.8</v>
+        <v>95.3</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -4003,7 +4003,7 @@
         <v>98</v>
       </c>
       <c r="U8">
-        <v>93.8</v>
+        <v>95.3</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -4050,7 +4050,7 @@
         <v>66.7</v>
       </c>
       <c r="N9">
-        <v>66.2</v>
+        <v>67.2</v>
       </c>
       <c r="O9">
         <v>38.3</v>
@@ -4071,7 +4071,7 @@
         <v>66.7</v>
       </c>
       <c r="U9">
-        <v>66.2</v>
+        <v>67.2</v>
       </c>
       <c r="V9">
         <v>38.3</v>
@@ -4118,7 +4118,7 @@
         <v>90.2</v>
       </c>
       <c r="N10">
-        <v>95.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O10">
         <v>100</v>
@@ -4139,7 +4139,7 @@
         <v>90.2</v>
       </c>
       <c r="U10">
-        <v>95.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V10">
         <v>100</v>
@@ -4186,7 +4186,7 @@
         <v>96.09999999999999</v>
       </c>
       <c r="N11">
-        <v>95.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O11">
         <v>100</v>
@@ -4207,7 +4207,7 @@
         <v>96.09999999999999</v>
       </c>
       <c r="U11">
-        <v>95.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V11">
         <v>100</v>
@@ -4254,7 +4254,7 @@
         <v>96.09999999999999</v>
       </c>
       <c r="N12">
-        <v>95.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O12">
         <v>91.7</v>
@@ -4275,7 +4275,7 @@
         <v>96.09999999999999</v>
       </c>
       <c r="U12">
-        <v>95.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V12">
         <v>91.7</v>
@@ -4322,7 +4322,7 @@
         <v>96.09999999999999</v>
       </c>
       <c r="N13">
-        <v>98.5</v>
+        <v>100</v>
       </c>
       <c r="O13">
         <v>100</v>
@@ -4343,7 +4343,7 @@
         <v>96.09999999999999</v>
       </c>
       <c r="U13">
-        <v>98.5</v>
+        <v>100</v>
       </c>
       <c r="V13">
         <v>100</v>
@@ -4390,7 +4390,7 @@
         <v>96.09999999999999</v>
       </c>
       <c r="N14">
-        <v>93.8</v>
+        <v>95.3</v>
       </c>
       <c r="O14">
         <v>100</v>
@@ -4411,7 +4411,7 @@
         <v>96.09999999999999</v>
       </c>
       <c r="U14">
-        <v>93.8</v>
+        <v>95.3</v>
       </c>
       <c r="V14">
         <v>100</v>
@@ -4458,7 +4458,7 @@
         <v>88.2</v>
       </c>
       <c r="N15">
-        <v>86.2</v>
+        <v>87.5</v>
       </c>
       <c r="O15">
         <v>88.3</v>
@@ -4479,7 +4479,7 @@
         <v>88.2</v>
       </c>
       <c r="U15">
-        <v>86.2</v>
+        <v>87.5</v>
       </c>
       <c r="V15">
         <v>88.3</v>
@@ -4526,7 +4526,7 @@
         <v>86.3</v>
       </c>
       <c r="N16">
-        <v>90.8</v>
+        <v>92.2</v>
       </c>
       <c r="O16">
         <v>88.3</v>
@@ -4547,7 +4547,7 @@
         <v>86.3</v>
       </c>
       <c r="U16">
-        <v>90.8</v>
+        <v>92.2</v>
       </c>
       <c r="V16">
         <v>88.3</v>
@@ -4594,7 +4594,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="N17">
-        <v>95.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O17">
         <v>100</v>
@@ -4615,7 +4615,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="U17">
-        <v>95.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -4662,7 +4662,7 @@
         <v>88.2</v>
       </c>
       <c r="N18">
-        <v>95.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O18">
         <v>100</v>
@@ -4683,7 +4683,7 @@
         <v>88.2</v>
       </c>
       <c r="U18">
-        <v>95.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -4730,7 +4730,7 @@
         <v>84.3</v>
       </c>
       <c r="N19">
-        <v>93.8</v>
+        <v>95.3</v>
       </c>
       <c r="O19">
         <v>100</v>
@@ -4751,7 +4751,7 @@
         <v>84.3</v>
       </c>
       <c r="U19">
-        <v>93.8</v>
+        <v>95.3</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -4798,7 +4798,7 @@
         <v>88.2</v>
       </c>
       <c r="N20">
-        <v>89.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O20">
         <v>100</v>
@@ -4819,7 +4819,7 @@
         <v>88.2</v>
       </c>
       <c r="U20">
-        <v>89.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -4866,7 +4866,7 @@
         <v>78.40000000000001</v>
       </c>
       <c r="N21">
-        <v>83.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="O21">
         <v>90</v>
@@ -4887,7 +4887,7 @@
         <v>78.40000000000001</v>
       </c>
       <c r="U21">
-        <v>83.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="V21">
         <v>90</v>
@@ -4934,7 +4934,7 @@
         <v>78.40000000000001</v>
       </c>
       <c r="N22">
-        <v>84.59999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="O22">
         <v>83.3</v>
@@ -4955,7 +4955,7 @@
         <v>78.40000000000001</v>
       </c>
       <c r="U22">
-        <v>84.59999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="V22">
         <v>83.3</v>
@@ -5002,7 +5002,7 @@
         <v>98</v>
       </c>
       <c r="N23">
-        <v>96.90000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O23">
         <v>100</v>
@@ -5023,7 +5023,7 @@
         <v>98</v>
       </c>
       <c r="U23">
-        <v>96.90000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V23">
         <v>100</v>
@@ -5070,7 +5070,7 @@
         <v>94.09999999999999</v>
       </c>
       <c r="N24">
-        <v>93.8</v>
+        <v>95.3</v>
       </c>
       <c r="O24">
         <v>91.7</v>
@@ -5091,7 +5091,7 @@
         <v>94.09999999999999</v>
       </c>
       <c r="U24">
-        <v>93.8</v>
+        <v>95.3</v>
       </c>
       <c r="V24">
         <v>91.7</v>
@@ -5138,7 +5138,7 @@
         <v>96.09999999999999</v>
       </c>
       <c r="N25">
-        <v>95.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O25">
         <v>100</v>
@@ -5159,7 +5159,7 @@
         <v>96.09999999999999</v>
       </c>
       <c r="U25">
-        <v>95.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V25">
         <v>100</v>
@@ -5206,7 +5206,7 @@
         <v>92.2</v>
       </c>
       <c r="N26">
-        <v>92.3</v>
+        <v>93.8</v>
       </c>
       <c r="O26">
         <v>93.3</v>
@@ -5227,7 +5227,7 @@
         <v>92.2</v>
       </c>
       <c r="U26">
-        <v>92.3</v>
+        <v>93.8</v>
       </c>
       <c r="V26">
         <v>93.3</v>
@@ -5274,7 +5274,7 @@
         <v>94.09999999999999</v>
       </c>
       <c r="N27">
-        <v>92.3</v>
+        <v>93.8</v>
       </c>
       <c r="O27">
         <v>93.3</v>
@@ -5295,7 +5295,7 @@
         <v>94.09999999999999</v>
       </c>
       <c r="U27">
-        <v>92.3</v>
+        <v>93.8</v>
       </c>
       <c r="V27">
         <v>93.3</v>
@@ -5342,7 +5342,7 @@
         <v>96.09999999999999</v>
       </c>
       <c r="N28">
-        <v>95.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O28">
         <v>100</v>
@@ -5363,7 +5363,7 @@
         <v>96.09999999999999</v>
       </c>
       <c r="U28">
-        <v>95.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V28">
         <v>100</v>
@@ -5410,7 +5410,7 @@
         <v>94.09999999999999</v>
       </c>
       <c r="N29">
-        <v>95.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O29">
         <v>100</v>
@@ -5431,7 +5431,7 @@
         <v>94.09999999999999</v>
       </c>
       <c r="U29">
-        <v>95.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V29">
         <v>100</v>
@@ -5478,7 +5478,7 @@
         <v>86.3</v>
       </c>
       <c r="N30">
-        <v>89.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O30">
         <v>100</v>
@@ -5499,7 +5499,7 @@
         <v>86.3</v>
       </c>
       <c r="U30">
-        <v>89.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="V30">
         <v>100</v>
@@ -5546,7 +5546,7 @@
         <v>84.3</v>
       </c>
       <c r="N31">
-        <v>90.8</v>
+        <v>92.2</v>
       </c>
       <c r="O31">
         <v>100</v>
@@ -5567,7 +5567,7 @@
         <v>84.3</v>
       </c>
       <c r="U31">
-        <v>90.8</v>
+        <v>92.2</v>
       </c>
       <c r="V31">
         <v>100</v>
@@ -5614,7 +5614,7 @@
         <v>90.2</v>
       </c>
       <c r="N32">
-        <v>90.8</v>
+        <v>92.2</v>
       </c>
       <c r="O32">
         <v>100</v>
@@ -5635,7 +5635,7 @@
         <v>90.2</v>
       </c>
       <c r="U32">
-        <v>90.8</v>
+        <v>92.2</v>
       </c>
       <c r="V32">
         <v>100</v>
@@ -5682,7 +5682,7 @@
         <v>96.09999999999999</v>
       </c>
       <c r="N33">
-        <v>93.8</v>
+        <v>95.3</v>
       </c>
       <c r="O33">
         <v>100</v>
@@ -5703,7 +5703,7 @@
         <v>96.09999999999999</v>
       </c>
       <c r="U33">
-        <v>93.8</v>
+        <v>95.3</v>
       </c>
       <c r="V33">
         <v>100</v>
@@ -5750,7 +5750,7 @@
         <v>94.09999999999999</v>
       </c>
       <c r="N34">
-        <v>95.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O34">
         <v>100</v>
@@ -5771,7 +5771,7 @@
         <v>94.09999999999999</v>
       </c>
       <c r="U34">
-        <v>95.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="V34">
         <v>100</v>

--- a/grupos/4AEM - Estadisticos 20222.xlsx
+++ b/grupos/4AEM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
   <si>
     <t>Materia</t>
   </si>
@@ -197,15 +197,15 @@
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
+    <t>Medina Tolentino Elio</t>
+  </si>
+  <si>
+    <t>Torres Sánchez José Luis</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
-    <t>Torres Sánchez José Luis</t>
-  </si>
-  <si>
-    <t>Medina Tolentino Elio</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -221,21 +221,24 @@
     <t>EVANGELISTA</t>
   </si>
   <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>BAROJAS</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
     <t>LOYO</t>
   </si>
   <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>TERRAZAS</t>
   </si>
   <si>
@@ -245,21 +248,21 @@
     <t>DE LA LUZ</t>
   </si>
   <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
     <t>MONGE</t>
   </si>
   <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>NERI</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -269,19 +272,22 @@
     <t>JUAN GERARDO</t>
   </si>
   <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>YAHIR</t>
+  </si>
+  <si>
+    <t>JHOSUA LEVY</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
     <t>MIGUEL</t>
   </si>
   <si>
     <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>JHOSUA LEVY</t>
   </si>
   <si>
     <t>MARIA REYNA</t>
@@ -838,22 +844,22 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>6</v>
@@ -862,7 +868,7 @@
         <v>7</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z4">
         <v>10</v>
@@ -927,28 +933,28 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W5">
         <v>8</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y5">
         <v>10</v>
@@ -1016,22 +1022,22 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>6</v>
@@ -1040,19 +1046,19 @@
         <v>6</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z6">
         <v>7</v>
       </c>
       <c r="AA6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC6">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1105,22 +1111,22 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S7">
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W7">
         <v>6</v>
@@ -1129,16 +1135,16 @@
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z7">
         <v>6</v>
       </c>
       <c r="AA7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC7">
         <v>9</v>
@@ -1194,22 +1200,22 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S8">
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>7</v>
@@ -1218,7 +1224,7 @@
         <v>10</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z8">
         <v>10</v>
@@ -1283,22 +1289,22 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W9">
         <v>5</v>
@@ -1307,16 +1313,16 @@
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z9">
         <v>5</v>
       </c>
       <c r="AA9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC9">
         <v>5</v>
@@ -1372,22 +1378,22 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S10">
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>5</v>
@@ -1396,16 +1402,16 @@
         <v>5</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z10">
         <v>6</v>
       </c>
       <c r="AA10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC10">
         <v>7</v>
@@ -1461,22 +1467,22 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S11">
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -1485,16 +1491,16 @@
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z11">
         <v>10</v>
       </c>
       <c r="AA11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC11">
         <v>10</v>
@@ -1550,22 +1556,22 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S12">
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>5</v>
@@ -1574,7 +1580,7 @@
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z12">
         <v>5</v>
@@ -1586,7 +1592,7 @@
         <v>8</v>
       </c>
       <c r="AC12">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1639,22 +1645,22 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W13">
         <v>7</v>
@@ -1663,7 +1669,7 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z13">
         <v>10</v>
@@ -1728,22 +1734,22 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -1752,7 +1758,7 @@
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z14">
         <v>9</v>
@@ -1817,22 +1823,22 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S15">
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>5</v>
@@ -1841,19 +1847,19 @@
         <v>5</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z15">
         <v>5</v>
       </c>
       <c r="AA15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC15">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1906,40 +1912,40 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>5</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z16">
         <v>6</v>
       </c>
       <c r="AA16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC16">
         <v>7</v>
@@ -1995,22 +2001,22 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>5</v>
@@ -2025,13 +2031,13 @@
         <v>7</v>
       </c>
       <c r="AA17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC17">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2084,43 +2090,43 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S18">
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>5</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z18">
         <v>7</v>
       </c>
       <c r="AA18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC18">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2173,22 +2179,22 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S19">
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W19">
         <v>5</v>
@@ -2197,19 +2203,19 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z19">
         <v>5</v>
       </c>
       <c r="AA19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC19">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2262,40 +2268,40 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>6</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z20">
         <v>10</v>
       </c>
       <c r="AA20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC20">
         <v>8</v>
@@ -2351,22 +2357,22 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S21">
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>5</v>
@@ -2375,16 +2381,16 @@
         <v>5</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z21">
         <v>5</v>
       </c>
       <c r="AA21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC21">
         <v>7</v>
@@ -2440,22 +2446,22 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S22">
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>5</v>
@@ -2464,19 +2470,19 @@
         <v>5</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z22">
         <v>7</v>
       </c>
       <c r="AA22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC22">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2529,22 +2535,22 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>7</v>
@@ -2553,19 +2559,19 @@
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z23">
         <v>7</v>
       </c>
       <c r="AA23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC23">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2618,43 +2624,43 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S24">
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>5</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z24">
         <v>5</v>
       </c>
       <c r="AA24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC24">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2707,31 +2713,31 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S25">
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>6</v>
       </c>
       <c r="X25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z25">
         <v>10</v>
@@ -2796,43 +2802,43 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W26">
         <v>5</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z26">
         <v>5</v>
       </c>
       <c r="AA26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB26">
         <v>7</v>
       </c>
       <c r="AC26">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2885,22 +2891,22 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S27">
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W27">
         <v>6</v>
@@ -2909,7 +2915,7 @@
         <v>6</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z27">
         <v>7</v>
@@ -2921,7 +2927,7 @@
         <v>9</v>
       </c>
       <c r="AC27">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -2974,31 +2980,31 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S28">
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>7</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z28">
         <v>9</v>
@@ -3063,31 +3069,31 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S29">
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>8</v>
       </c>
       <c r="X29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z29">
         <v>10</v>
@@ -3152,22 +3158,22 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S30">
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W30">
         <v>5</v>
@@ -3182,10 +3188,10 @@
         <v>8</v>
       </c>
       <c r="AA30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC30">
         <v>9</v>
@@ -3241,22 +3247,22 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S31">
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>5</v>
@@ -3265,16 +3271,16 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z31">
         <v>6</v>
       </c>
       <c r="AA31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC31">
         <v>9</v>
@@ -3330,40 +3336,40 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S32">
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W32">
         <v>7</v>
       </c>
       <c r="X32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z32">
         <v>7</v>
       </c>
       <c r="AA32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC32">
         <v>9</v>
@@ -3419,40 +3425,40 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S33">
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W33">
         <v>6</v>
       </c>
       <c r="X33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z33">
         <v>8</v>
       </c>
       <c r="AA33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC33">
         <v>9</v>
@@ -3508,22 +3514,22 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S34">
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W34">
         <v>7</v>
@@ -3532,7 +3538,7 @@
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z34">
         <v>10</v>
@@ -3728,10 +3734,10 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>98</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="U4">
-        <v>95.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="V4">
         <v>100</v>
@@ -3799,7 +3805,7 @@
         <v>100</v>
       </c>
       <c r="U5">
-        <v>96.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -3864,10 +3870,10 @@
         <v>100</v>
       </c>
       <c r="T6">
-        <v>82.40000000000001</v>
+        <v>87</v>
       </c>
       <c r="U6">
-        <v>84.40000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="V6">
         <v>100</v>
@@ -3923,19 +3929,19 @@
         <v>90</v>
       </c>
       <c r="Q7">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R7">
-        <v>65</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="S7">
         <v>100</v>
       </c>
       <c r="T7">
-        <v>88.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U7">
-        <v>84.40000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="V7">
         <v>100</v>
@@ -4000,10 +4006,10 @@
         <v>100</v>
       </c>
       <c r="T8">
-        <v>98</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="U8">
-        <v>95.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -4059,22 +4065,22 @@
         <v>40</v>
       </c>
       <c r="Q9">
-        <v>30</v>
+        <v>18.8</v>
       </c>
       <c r="R9">
-        <v>65</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="S9">
         <v>50</v>
       </c>
       <c r="T9">
-        <v>66.7</v>
+        <v>44.2</v>
       </c>
       <c r="U9">
-        <v>67.2</v>
+        <v>46.2</v>
       </c>
       <c r="V9">
-        <v>38.3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -4127,7 +4133,7 @@
         <v>97.5</v>
       </c>
       <c r="Q10">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R10">
         <v>100</v>
@@ -4136,10 +4142,10 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>90.2</v>
+        <v>93.5</v>
       </c>
       <c r="U10">
-        <v>96.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="V10">
         <v>100</v>
@@ -4207,7 +4213,7 @@
         <v>96.09999999999999</v>
       </c>
       <c r="U11">
-        <v>96.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="V11">
         <v>100</v>
@@ -4263,10 +4269,10 @@
         <v>87.5</v>
       </c>
       <c r="Q12">
-        <v>82.5</v>
+        <v>82.8</v>
       </c>
       <c r="R12">
-        <v>67.5</v>
+        <v>79.7</v>
       </c>
       <c r="S12">
         <v>90.59999999999999</v>
@@ -4275,10 +4281,10 @@
         <v>96.09999999999999</v>
       </c>
       <c r="U12">
-        <v>96.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="V12">
-        <v>91.7</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -4331,7 +4337,7 @@
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="R13">
         <v>100</v>
@@ -4408,10 +4414,10 @@
         <v>100</v>
       </c>
       <c r="T14">
-        <v>96.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="U14">
-        <v>95.3</v>
+        <v>97.8</v>
       </c>
       <c r="V14">
         <v>100</v>
@@ -4467,22 +4473,22 @@
         <v>87.5</v>
       </c>
       <c r="Q15">
-        <v>82.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="R15">
-        <v>57.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="S15">
         <v>87.5</v>
       </c>
       <c r="T15">
-        <v>88.2</v>
+        <v>92.2</v>
       </c>
       <c r="U15">
-        <v>87.5</v>
+        <v>93.5</v>
       </c>
       <c r="V15">
-        <v>88.3</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -4535,22 +4541,22 @@
         <v>82.5</v>
       </c>
       <c r="Q16">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="R16">
-        <v>72.5</v>
+        <v>82.8</v>
       </c>
       <c r="S16">
         <v>90.59999999999999</v>
       </c>
       <c r="T16">
-        <v>86.3</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="U16">
-        <v>92.2</v>
+        <v>95.7</v>
       </c>
       <c r="V16">
-        <v>88.3</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -4603,19 +4609,19 @@
         <v>80</v>
       </c>
       <c r="Q17">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="R17">
-        <v>77.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S17">
         <v>90.59999999999999</v>
       </c>
       <c r="T17">
-        <v>82.40000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="U17">
-        <v>96.90000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -4680,10 +4686,10 @@
         <v>100</v>
       </c>
       <c r="T18">
-        <v>88.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U18">
-        <v>96.90000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -4739,19 +4745,19 @@
         <v>87.5</v>
       </c>
       <c r="Q19">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="R19">
-        <v>65</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="S19">
         <v>100</v>
       </c>
       <c r="T19">
-        <v>84.3</v>
+        <v>88.3</v>
       </c>
       <c r="U19">
-        <v>95.3</v>
+        <v>97.8</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -4807,7 +4813,7 @@
         <v>85</v>
       </c>
       <c r="Q20">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R20">
         <v>100</v>
@@ -4816,10 +4822,10 @@
         <v>100</v>
       </c>
       <c r="T20">
-        <v>88.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U20">
-        <v>90.59999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -4875,22 +4881,22 @@
         <v>82.5</v>
       </c>
       <c r="Q21">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R21">
-        <v>70</v>
+        <v>81.3</v>
       </c>
       <c r="S21">
         <v>100</v>
       </c>
       <c r="T21">
-        <v>78.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="U21">
-        <v>84.40000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="V21">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -4943,22 +4949,22 @@
         <v>82.5</v>
       </c>
       <c r="Q22">
-        <v>90</v>
+        <v>82.8</v>
       </c>
       <c r="R22">
-        <v>52.5</v>
+        <v>70.3</v>
       </c>
       <c r="S22">
         <v>90.59999999999999</v>
       </c>
       <c r="T22">
-        <v>78.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="U22">
-        <v>85.90000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="V22">
-        <v>83.3</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -5020,10 +5026,10 @@
         <v>100</v>
       </c>
       <c r="T23">
-        <v>98</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="U23">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="V23">
         <v>100</v>
@@ -5079,7 +5085,7 @@
         <v>75</v>
       </c>
       <c r="Q24">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R24">
         <v>100</v>
@@ -5088,13 +5094,13 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>94.09999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="U24">
-        <v>95.3</v>
+        <v>97.8</v>
       </c>
       <c r="V24">
-        <v>91.7</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -5156,10 +5162,10 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>96.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="U25">
-        <v>96.90000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="V25">
         <v>100</v>
@@ -5224,13 +5230,13 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>92.2</v>
+        <v>93.5</v>
       </c>
       <c r="U26">
-        <v>93.8</v>
+        <v>95.7</v>
       </c>
       <c r="V26">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -5286,19 +5292,19 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>77.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S27">
         <v>100</v>
       </c>
       <c r="T27">
-        <v>94.09999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="U27">
-        <v>93.8</v>
+        <v>97.8</v>
       </c>
       <c r="V27">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -5360,10 +5366,10 @@
         <v>100</v>
       </c>
       <c r="T28">
-        <v>96.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="U28">
-        <v>96.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="V28">
         <v>100</v>
@@ -5428,10 +5434,10 @@
         <v>100</v>
       </c>
       <c r="T29">
-        <v>94.09999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="U29">
-        <v>96.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="V29">
         <v>100</v>
@@ -5496,10 +5502,10 @@
         <v>100</v>
       </c>
       <c r="T30">
-        <v>86.3</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="U30">
-        <v>90.59999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="V30">
         <v>100</v>
@@ -5555,7 +5561,7 @@
         <v>85</v>
       </c>
       <c r="Q31">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="R31">
         <v>100</v>
@@ -5564,10 +5570,10 @@
         <v>100</v>
       </c>
       <c r="T31">
-        <v>84.3</v>
+        <v>88.3</v>
       </c>
       <c r="U31">
-        <v>92.2</v>
+        <v>95.7</v>
       </c>
       <c r="V31">
         <v>100</v>
@@ -5632,10 +5638,10 @@
         <v>100</v>
       </c>
       <c r="T32">
-        <v>90.2</v>
+        <v>93.5</v>
       </c>
       <c r="U32">
-        <v>92.2</v>
+        <v>96.8</v>
       </c>
       <c r="V32">
         <v>100</v>
@@ -5700,10 +5706,10 @@
         <v>100</v>
       </c>
       <c r="T33">
-        <v>96.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="U33">
-        <v>95.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="V33">
         <v>100</v>
@@ -5768,10 +5774,10 @@
         <v>100</v>
       </c>
       <c r="T34">
-        <v>94.09999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="U34">
-        <v>96.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="V34">
         <v>100</v>
@@ -5872,19 +5878,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>74.2</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>25.8</v>
+        <v>22.6</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5927,7 +5933,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
@@ -5936,19 +5942,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2">
-        <v>83.90000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>16.1</v>
+        <v>19.4</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5968,19 +5974,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>93.5</v>
+        <v>96.8</v>
       </c>
       <c r="G6" s="2">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5991,28 +5997,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C7">
         <v>31</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>93.5</v>
+        <v>96.8</v>
       </c>
       <c r="G7" s="2">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6023,28 +6029,28 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8">
         <v>31</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="G8" s="2">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6094,7 +6100,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6132,10 +6138,10 @@
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6155,10 +6161,10 @@
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -6172,16 +6178,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920163</v>
+        <v>21330051920165</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -6195,16 +6201,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920163</v>
+        <v>21330051920165</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -6218,16 +6224,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920164</v>
+        <v>21330051920171</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -6241,22 +6247,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920164</v>
+        <v>21330051920171</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6264,16 +6270,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920166</v>
+        <v>21330051920175</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -6287,16 +6293,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920166</v>
+        <v>21330051920175</v>
       </c>
       <c r="B9" t="s">
         <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -6310,22 +6316,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920171</v>
+        <v>21330051920154</v>
       </c>
       <c r="B10" t="s">
         <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -6333,22 +6339,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920171</v>
+        <v>21330051920163</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -6356,16 +6362,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920175</v>
+        <v>21330051920164</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
@@ -6379,22 +6385,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920175</v>
+        <v>21330051920180</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -6402,16 +6408,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920180</v>
+        <v>21330051920181</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -6420,29 +6426,6 @@
         <v>56</v>
       </c>
       <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920181</v>
-      </c>
-      <c r="B15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" t="s">
-        <v>89</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4AEM - Estadisticos 20222.xlsx
+++ b/grupos/4AEM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="96">
   <si>
     <t>Materia</t>
   </si>
@@ -188,18 +188,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
+    <t>Medina Tolentino Elio</t>
+  </si>
+  <si>
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
-    <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
-    <t>Medina Tolentino Elio</t>
-  </si>
-  <si>
     <t>Torres Sánchez José Luis</t>
   </si>
   <si>
@@ -218,82 +218,94 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>BAROJAS</t>
+  </si>
+  <si>
     <t>EVANGELISTA</t>
   </si>
   <si>
-    <t>LORENZO</t>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>MAYO</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
   </si>
   <si>
     <t>MOLOHUA</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>BAROJAS</t>
+    <t>TERRAZAS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>MONGE</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>NERI</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>LOYO</t>
-  </si>
-  <si>
-    <t>TERRAZAS</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
     <t>MIXCOHUA</t>
   </si>
   <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
+    <t>CRISTIAN FERNANDO</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>JHOSUA LEVY</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
   </si>
   <si>
     <t>JUAN GERARDO</t>
   </si>
   <si>
-    <t>ROBERTO</t>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>LUIS OMAR</t>
+  </si>
+  <si>
+    <t>SALVADOR</t>
   </si>
   <si>
     <t>YAHIR</t>
   </si>
   <si>
-    <t>JHOSUA LEVY</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
     <t>MARIA REYNA</t>
-  </si>
-  <si>
-    <t>ADALY</t>
   </si>
 </sst>
 </file>
@@ -841,7 +853,7 @@
         <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
         <v>6</v>
@@ -850,7 +862,7 @@
         <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -930,7 +942,7 @@
         <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
         <v>7</v>
@@ -939,7 +951,7 @@
         <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -1019,7 +1031,7 @@
         <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
         <v>7</v>
@@ -1028,7 +1040,7 @@
         <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -1108,7 +1120,7 @@
         <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
         <v>8</v>
@@ -1117,7 +1129,7 @@
         <v>6</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1138,7 +1150,7 @@
         <v>5</v>
       </c>
       <c r="Z7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA7">
         <v>8</v>
@@ -1197,7 +1209,7 @@
         <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
         <v>10</v>
@@ -1206,7 +1218,7 @@
         <v>6</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1286,7 +1298,7 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
         <v>5</v>
@@ -1295,7 +1307,7 @@
         <v>6</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
         <v>5</v>
@@ -1375,7 +1387,7 @@
         <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
         <v>6</v>
@@ -1384,7 +1396,7 @@
         <v>6</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -1396,7 +1408,7 @@
         <v>7</v>
       </c>
       <c r="W10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X10">
         <v>5</v>
@@ -1464,7 +1476,7 @@
         <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
         <v>10</v>
@@ -1473,7 +1485,7 @@
         <v>6</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1485,7 +1497,7 @@
         <v>10</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -1553,7 +1565,7 @@
         <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
         <v>5</v>
@@ -1562,7 +1574,7 @@
         <v>6</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1574,7 +1586,7 @@
         <v>9</v>
       </c>
       <c r="W12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>5</v>
@@ -1642,7 +1654,7 @@
         <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
         <v>10</v>
@@ -1651,7 +1663,7 @@
         <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -1731,7 +1743,7 @@
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
         <v>9</v>
@@ -1740,7 +1752,7 @@
         <v>6</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1820,7 +1832,7 @@
         <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
         <v>6</v>
@@ -1829,7 +1841,7 @@
         <v>6</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>9</v>
@@ -1841,7 +1853,7 @@
         <v>9</v>
       </c>
       <c r="W15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -1850,7 +1862,7 @@
         <v>5</v>
       </c>
       <c r="Z15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA15">
         <v>6</v>
@@ -1909,7 +1921,7 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
         <v>7</v>
@@ -1918,7 +1930,7 @@
         <v>6</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -1930,7 +1942,7 @@
         <v>9</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>6</v>
@@ -1939,7 +1951,7 @@
         <v>7</v>
       </c>
       <c r="Z16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA16">
         <v>7</v>
@@ -1998,7 +2010,7 @@
         <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
         <v>6</v>
@@ -2007,7 +2019,7 @@
         <v>6</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
         <v>9</v>
@@ -2028,7 +2040,7 @@
         <v>7</v>
       </c>
       <c r="Z17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA17">
         <v>7</v>
@@ -2087,7 +2099,7 @@
         <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
         <v>5</v>
@@ -2096,7 +2108,7 @@
         <v>6</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T18">
         <v>9</v>
@@ -2108,7 +2120,7 @@
         <v>8</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>6</v>
@@ -2176,7 +2188,7 @@
         <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
         <v>8</v>
@@ -2185,7 +2197,7 @@
         <v>6</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -2197,7 +2209,7 @@
         <v>10</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>7</v>
@@ -2206,7 +2218,7 @@
         <v>5</v>
       </c>
       <c r="Z19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA19">
         <v>8</v>
@@ -2265,7 +2277,7 @@
         <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
         <v>5</v>
@@ -2274,7 +2286,7 @@
         <v>6</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>9</v>
@@ -2286,7 +2298,7 @@
         <v>9</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X20">
         <v>6</v>
@@ -2354,7 +2366,7 @@
         <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
         <v>6</v>
@@ -2363,7 +2375,7 @@
         <v>6</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>9</v>
@@ -2375,7 +2387,7 @@
         <v>7</v>
       </c>
       <c r="W21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>5</v>
@@ -2384,7 +2396,7 @@
         <v>7</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA21">
         <v>7</v>
@@ -2443,7 +2455,7 @@
         <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -2452,7 +2464,7 @@
         <v>6</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
         <v>9</v>
@@ -2473,7 +2485,7 @@
         <v>5</v>
       </c>
       <c r="Z22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA22">
         <v>7</v>
@@ -2532,7 +2544,7 @@
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
         <v>10</v>
@@ -2541,7 +2553,7 @@
         <v>6</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>10</v>
@@ -2553,7 +2565,7 @@
         <v>7</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -2621,7 +2633,7 @@
         <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
         <v>5</v>
@@ -2630,7 +2642,7 @@
         <v>6</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2642,7 +2654,7 @@
         <v>9</v>
       </c>
       <c r="W24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X24">
         <v>6</v>
@@ -2710,7 +2722,7 @@
         <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
         <v>7</v>
@@ -2719,7 +2731,7 @@
         <v>6</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2740,7 +2752,7 @@
         <v>7</v>
       </c>
       <c r="Z25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA25">
         <v>8</v>
@@ -2799,7 +2811,7 @@
         <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q26">
         <v>5</v>
@@ -2808,7 +2820,7 @@
         <v>6</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -2888,7 +2900,7 @@
         <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
         <v>6</v>
@@ -2897,7 +2909,7 @@
         <v>6</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2909,7 +2921,7 @@
         <v>10</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>6</v>
@@ -2918,7 +2930,7 @@
         <v>7</v>
       </c>
       <c r="Z27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA27">
         <v>9</v>
@@ -2977,7 +2989,7 @@
         <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
         <v>7</v>
@@ -2986,7 +2998,7 @@
         <v>6</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -3007,7 +3019,7 @@
         <v>7</v>
       </c>
       <c r="Z28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA28">
         <v>9</v>
@@ -3066,7 +3078,7 @@
         <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
         <v>7</v>
@@ -3075,7 +3087,7 @@
         <v>6</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>10</v>
@@ -3087,7 +3099,7 @@
         <v>9</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>9</v>
@@ -3155,7 +3167,7 @@
         <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
         <v>10</v>
@@ -3164,7 +3176,7 @@
         <v>7</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -3244,7 +3256,7 @@
         <v>9</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
         <v>7</v>
@@ -3253,7 +3265,7 @@
         <v>6</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -3265,7 +3277,7 @@
         <v>9</v>
       </c>
       <c r="W31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X31">
         <v>7</v>
@@ -3333,7 +3345,7 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q32">
         <v>6</v>
@@ -3342,7 +3354,7 @@
         <v>6</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
         <v>10</v>
@@ -3422,7 +3434,7 @@
         <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q33">
         <v>8</v>
@@ -3431,7 +3443,7 @@
         <v>6</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3452,7 +3464,7 @@
         <v>7</v>
       </c>
       <c r="Z33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA33">
         <v>8</v>
@@ -3511,7 +3523,7 @@
         <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q34">
         <v>9</v>
@@ -3520,7 +3532,7 @@
         <v>6</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>10</v>
@@ -3722,7 +3734,7 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -3790,7 +3802,7 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -3858,7 +3870,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -3926,7 +3938,7 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q7">
         <v>96.90000000000001</v>
@@ -3994,7 +4006,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -4062,7 +4074,7 @@
         <v>38.3</v>
       </c>
       <c r="P9">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="Q9">
         <v>18.8</v>
@@ -4071,7 +4083,7 @@
         <v>78.09999999999999</v>
       </c>
       <c r="S9">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="T9">
         <v>44.2</v>
@@ -4130,7 +4142,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q10">
         <v>98.40000000000001</v>
@@ -4198,7 +4210,7 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -4266,7 +4278,7 @@
         <v>91.7</v>
       </c>
       <c r="P12">
-        <v>87.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q12">
         <v>82.8</v>
@@ -4275,7 +4287,7 @@
         <v>79.7</v>
       </c>
       <c r="S12">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="T12">
         <v>96.09999999999999</v>
@@ -4470,7 +4482,7 @@
         <v>88.3</v>
       </c>
       <c r="P15">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="Q15">
         <v>89.09999999999999</v>
@@ -4479,7 +4491,7 @@
         <v>73.40000000000001</v>
       </c>
       <c r="S15">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="T15">
         <v>92.2</v>
@@ -4538,7 +4550,7 @@
         <v>88.3</v>
       </c>
       <c r="P16">
-        <v>82.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q16">
         <v>95.3</v>
@@ -4547,7 +4559,7 @@
         <v>82.8</v>
       </c>
       <c r="S16">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="T16">
         <v>89.59999999999999</v>
@@ -4606,7 +4618,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>80</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q17">
         <v>92.2</v>
@@ -4615,7 +4627,7 @@
         <v>85.90000000000001</v>
       </c>
       <c r="S17">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="T17">
         <v>88.3</v>
@@ -4674,7 +4686,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -4742,7 +4754,7 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="Q19">
         <v>95.3</v>
@@ -4810,7 +4822,7 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>85</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q20">
         <v>93.8</v>
@@ -4878,7 +4890,7 @@
         <v>90</v>
       </c>
       <c r="P21">
-        <v>82.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q21">
         <v>93.8</v>
@@ -4946,7 +4958,7 @@
         <v>83.3</v>
       </c>
       <c r="P22">
-        <v>82.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q22">
         <v>82.8</v>
@@ -4955,7 +4967,7 @@
         <v>70.3</v>
       </c>
       <c r="S22">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="T22">
         <v>85.7</v>
@@ -5014,7 +5026,7 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -5082,7 +5094,7 @@
         <v>91.7</v>
       </c>
       <c r="P24">
-        <v>75</v>
+        <v>82.8</v>
       </c>
       <c r="Q24">
         <v>96.90000000000001</v>
@@ -5150,7 +5162,7 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q25">
         <v>100</v>
@@ -5218,7 +5230,7 @@
         <v>93.3</v>
       </c>
       <c r="P26">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -5286,7 +5298,7 @@
         <v>93.3</v>
       </c>
       <c r="P27">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -5354,7 +5366,7 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -5422,7 +5434,7 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -5490,7 +5502,7 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -5558,7 +5570,7 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="Q31">
         <v>92.2</v>
@@ -5626,7 +5638,7 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q32">
         <v>100</v>
@@ -5694,7 +5706,7 @@
         <v>100</v>
       </c>
       <c r="P33">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q33">
         <v>100</v>
@@ -5837,7 +5849,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>
@@ -5846,19 +5858,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2">
-        <v>54.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>45.2</v>
+        <v>22.6</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5869,7 +5881,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
@@ -5878,19 +5890,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" s="2">
-        <v>77.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>22.6</v>
+        <v>19.4</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5901,7 +5913,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -5910,19 +5922,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2">
-        <v>77.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>22.6</v>
+        <v>19.4</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>6.2</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5933,7 +5945,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
@@ -5942,19 +5954,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>80.59999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>19.4</v>
+        <v>12.9</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6132,19 +6144,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920156</v>
+        <v>21330051920162</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>56</v>
@@ -6155,19 +6167,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920156</v>
+        <v>21330051920162</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
         <v>57</v>
@@ -6184,16 +6196,16 @@
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6207,16 +6219,16 @@
         <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6224,22 +6236,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920171</v>
+        <v>21330051920175</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6247,22 +6259,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920171</v>
+        <v>21330051920175</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6270,22 +6282,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920175</v>
+        <v>21330051920154</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6293,22 +6305,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920175</v>
+        <v>21330051920156</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6316,22 +6328,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920154</v>
+        <v>21330051920166</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -6339,22 +6351,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920163</v>
+        <v>21330051920167</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
         <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -6362,19 +6374,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920164</v>
+        <v>21330051920168</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
         <v>56</v>
@@ -6385,22 +6397,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920180</v>
+        <v>21330051920171</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -6408,22 +6420,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920181</v>
+        <v>21330051920180</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G14">
         <v>5</v>
